--- a/example_data.xlsx
+++ b/example_data.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shank\Desktop\DZ Studio\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9AF9149-274A-4908-AA07-C28432CC8C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ZrUPb" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -25,29 +31,29 @@
     <t>BestAge errors</t>
   </si>
   <si>
-    <t>WBS Fluvial</t>
+    <t>A</t>
   </si>
   <si>
-    <t>WBS Eolian</t>
+    <t>B</t>
   </si>
   <si>
-    <t>TSA 1</t>
+    <t>C</t>
   </si>
   <si>
-    <t>TSA 2</t>
+    <t>D</t>
   </si>
   <si>
-    <t>TSA 3</t>
+    <t>E</t>
   </si>
   <si>
-    <t>TSA 4</t>
+    <t>F</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,13 +90,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -128,7 +142,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -162,6 +176,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -196,9 +211,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -371,11 +387,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C713"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="9.9296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.265625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -386,7 +407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -394,10 +415,10 @@
         <v>1172.46</v>
       </c>
       <c r="C2">
-        <v>35.2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>35.200000000000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -408,18 +429,18 @@
         <v>14.42</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1075.09</v>
+        <v>1075.0899999999999</v>
       </c>
       <c r="C4">
         <v>25.62</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -430,7 +451,7 @@
         <v>34.31</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -441,7 +462,7 @@
         <v>24.78</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -452,7 +473,7 @@
         <v>32.97</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -463,7 +484,7 @@
         <v>17.48</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -471,10 +492,10 @@
         <v>1036.08</v>
       </c>
       <c r="C9">
-        <v>32.66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>32.659999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -485,18 +506,18 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>3</v>
       </c>
       <c r="B11">
-        <v>1249.38</v>
+        <v>1249.3800000000001</v>
       </c>
       <c r="C11">
         <v>48.36</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -507,29 +528,29 @@
         <v>18.84</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>3</v>
       </c>
       <c r="B13">
-        <v>1028.84</v>
+        <v>1028.8399999999999</v>
       </c>
       <c r="C13">
         <v>25.36</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>3</v>
       </c>
       <c r="B14">
-        <v>1033.12</v>
+        <v>1033.1199999999999</v>
       </c>
       <c r="C14">
         <v>35.56</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -540,18 +561,18 @@
         <v>25.67</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>3</v>
       </c>
       <c r="B16">
-        <v>986.6900000000001</v>
+        <v>986.69</v>
       </c>
       <c r="C16">
         <v>26.74</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -562,7 +583,7 @@
         <v>24.66</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -573,7 +594,7 @@
         <v>19.79</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -584,7 +605,7 @@
         <v>24.53</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -595,7 +616,7 @@
         <v>41.02</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -606,7 +627,7 @@
         <v>35.72</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -617,7 +638,7 @@
         <v>24.64</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -628,7 +649,7 @@
         <v>59.54</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -639,7 +660,7 @@
         <v>62.69</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -650,7 +671,7 @@
         <v>60.23</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -661,7 +682,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -672,7 +693,7 @@
         <v>35.65</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>3</v>
       </c>
@@ -683,7 +704,7 @@
         <v>73.44</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -694,7 +715,7 @@
         <v>39.33</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>3</v>
       </c>
@@ -705,7 +726,7 @@
         <v>60.11</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -716,7 +737,7 @@
         <v>56.66</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -727,7 +748,7 @@
         <v>62.34</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>3</v>
       </c>
@@ -738,7 +759,7 @@
         <v>30.92</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>3</v>
       </c>
@@ -746,10 +767,10 @@
         <v>1811.78</v>
       </c>
       <c r="C34">
-        <v>69.59999999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
+        <v>69.599999999999994</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>3</v>
       </c>
@@ -757,10 +778,10 @@
         <v>1790.62</v>
       </c>
       <c r="C35">
-        <v>66.29000000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
+        <v>66.290000000000006</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>3</v>
       </c>
@@ -771,7 +792,7 @@
         <v>38.15</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>3</v>
       </c>
@@ -782,7 +803,7 @@
         <v>59.41</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>3</v>
       </c>
@@ -793,7 +814,7 @@
         <v>25.06</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -804,7 +825,7 @@
         <v>66.97</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>3</v>
       </c>
@@ -815,7 +836,7 @@
         <v>43.67</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -826,7 +847,7 @@
         <v>55.16</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>3</v>
       </c>
@@ -837,7 +858,7 @@
         <v>62.07</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>3</v>
       </c>
@@ -848,7 +869,7 @@
         <v>29.93</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>3</v>
       </c>
@@ -859,7 +880,7 @@
         <v>63.89</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>3</v>
       </c>
@@ -870,7 +891,7 @@
         <v>31.01</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>3</v>
       </c>
@@ -881,7 +902,7 @@
         <v>34.54</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>3</v>
       </c>
@@ -892,7 +913,7 @@
         <v>47.07</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>3</v>
       </c>
@@ -903,7 +924,7 @@
         <v>40.82</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>3</v>
       </c>
@@ -914,7 +935,7 @@
         <v>56.87</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>3</v>
       </c>
@@ -925,7 +946,7 @@
         <v>36.28</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>3</v>
       </c>
@@ -936,7 +957,7 @@
         <v>56.57</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>3</v>
       </c>
@@ -947,7 +968,7 @@
         <v>59.5</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>3</v>
       </c>
@@ -958,7 +979,7 @@
         <v>104.25</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>3</v>
       </c>
@@ -966,10 +987,10 @@
         <v>2755.04</v>
       </c>
       <c r="C54">
-        <v>70.48999999999999</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
+        <v>70.489999999999995</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>3</v>
       </c>
@@ -980,7 +1001,7 @@
         <v>62.99</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>3</v>
       </c>
@@ -991,7 +1012,7 @@
         <v>80.84</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>3</v>
       </c>
@@ -1002,7 +1023,7 @@
         <v>84.55</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>3</v>
       </c>
@@ -1013,7 +1034,7 @@
         <v>104.3</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>3</v>
       </c>
@@ -1021,10 +1042,10 @@
         <v>2570.37</v>
       </c>
       <c r="C59">
-        <v>77.26000000000001</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
+        <v>77.260000000000005</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>3</v>
       </c>
@@ -1032,10 +1053,10 @@
         <v>2761.41</v>
       </c>
       <c r="C60">
-        <v>73.23999999999999</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
+        <v>73.239999999999995</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>3</v>
       </c>
@@ -1046,7 +1067,7 @@
         <v>63.63</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>3</v>
       </c>
@@ -1057,7 +1078,7 @@
         <v>87.58</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>3</v>
       </c>
@@ -1065,10 +1086,10 @@
         <v>2723.68</v>
       </c>
       <c r="C63">
-        <v>85.26000000000001</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
+        <v>85.26</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>3</v>
       </c>
@@ -1079,7 +1100,7 @@
         <v>47.17</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>3</v>
       </c>
@@ -1090,18 +1111,18 @@
         <v>64.11</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>3</v>
       </c>
       <c r="B66">
-        <v>2597.95</v>
+        <v>2597.9499999999998</v>
       </c>
       <c r="C66">
         <v>51.99</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>3</v>
       </c>
@@ -1112,7 +1133,7 @@
         <v>74.33</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>3</v>
       </c>
@@ -1123,7 +1144,7 @@
         <v>69.47</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>3</v>
       </c>
@@ -1134,7 +1155,7 @@
         <v>55.26</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>3</v>
       </c>
@@ -1145,7 +1166,7 @@
         <v>74.39</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>3</v>
       </c>
@@ -1156,7 +1177,7 @@
         <v>85.61</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>3</v>
       </c>
@@ -1164,10 +1185,10 @@
         <v>2739.68</v>
       </c>
       <c r="C72">
-        <v>66.26000000000001</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
+        <v>66.260000000000005</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>3</v>
       </c>
@@ -1175,10 +1196,10 @@
         <v>2683.45</v>
       </c>
       <c r="C73">
-        <v>96.68000000000001</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
+        <v>96.68</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>3</v>
       </c>
@@ -1189,7 +1210,7 @@
         <v>51.91</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>3</v>
       </c>
@@ -1200,7 +1221,7 @@
         <v>46.03</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>3</v>
       </c>
@@ -1208,10 +1229,10 @@
         <v>2741.27</v>
       </c>
       <c r="C76">
-        <v>90.40000000000001</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
+        <v>90.4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>3</v>
       </c>
@@ -1219,10 +1240,10 @@
         <v>2657.1</v>
       </c>
       <c r="C77">
-        <v>78.43000000000001</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
+        <v>78.430000000000007</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>3</v>
       </c>
@@ -1233,7 +1254,7 @@
         <v>95.47</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>3</v>
       </c>
@@ -1244,7 +1265,7 @@
         <v>104.49</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>3</v>
       </c>
@@ -1252,10 +1273,10 @@
         <v>2697.66</v>
       </c>
       <c r="C80">
-        <v>76.23999999999999</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
+        <v>76.239999999999995</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>3</v>
       </c>
@@ -1263,10 +1284,10 @@
         <v>2616.91</v>
       </c>
       <c r="C81">
-        <v>93.18000000000001</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
+        <v>93.18</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>3</v>
       </c>
@@ -1277,7 +1298,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>3</v>
       </c>
@@ -1288,7 +1309,7 @@
         <v>78.37</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>3</v>
       </c>
@@ -1299,7 +1320,7 @@
         <v>77.64</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>3</v>
       </c>
@@ -1310,7 +1331,7 @@
         <v>110.99</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>3</v>
       </c>
@@ -1318,10 +1339,10 @@
         <v>2740.95</v>
       </c>
       <c r="C86">
-        <v>66.59999999999999</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3">
+        <v>66.599999999999994</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>3</v>
       </c>
@@ -1329,10 +1350,10 @@
         <v>2681.65</v>
       </c>
       <c r="C87">
-        <v>70.23999999999999</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3">
+        <v>70.239999999999995</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>3</v>
       </c>
@@ -1340,10 +1361,10 @@
         <v>2671.99</v>
       </c>
       <c r="C88">
-        <v>73.18000000000001</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
+        <v>73.180000000000007</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>3</v>
       </c>
@@ -1354,7 +1375,7 @@
         <v>83.78</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>3</v>
       </c>
@@ -1365,7 +1386,7 @@
         <v>48.94</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>3</v>
       </c>
@@ -1373,10 +1394,10 @@
         <v>2632.38</v>
       </c>
       <c r="C91">
-        <v>83.29000000000001</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
+        <v>83.29</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>3</v>
       </c>
@@ -1387,7 +1408,7 @@
         <v>45.42</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>3</v>
       </c>
@@ -1398,7 +1419,7 @@
         <v>67.81</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>3</v>
       </c>
@@ -1406,10 +1427,10 @@
         <v>2733.48</v>
       </c>
       <c r="C94">
-        <v>72.76000000000001</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3">
+        <v>72.760000000000005</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>3</v>
       </c>
@@ -1417,10 +1438,10 @@
         <v>2754.52</v>
       </c>
       <c r="C95">
-        <v>81.48999999999999</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3">
+        <v>81.489999999999995</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>3</v>
       </c>
@@ -1431,18 +1452,18 @@
         <v>78.61</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>3</v>
       </c>
       <c r="B97">
-        <v>2616.2</v>
+        <v>2616.1999999999998</v>
       </c>
       <c r="C97">
-        <v>79.76000000000001</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3">
+        <v>79.760000000000005</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>3</v>
       </c>
@@ -1453,7 +1474,7 @@
         <v>45.12</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>3</v>
       </c>
@@ -1461,10 +1482,10 @@
         <v>2792.81</v>
       </c>
       <c r="C99">
-        <v>66.70999999999999</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3">
+        <v>66.709999999999994</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>3</v>
       </c>
@@ -1475,7 +1496,7 @@
         <v>93.23</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>3</v>
       </c>
@@ -1486,7 +1507,7 @@
         <v>71.09</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>3</v>
       </c>
@@ -1497,7 +1518,7 @@
         <v>96.78</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>3</v>
       </c>
@@ -1508,7 +1529,7 @@
         <v>79.52</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>3</v>
       </c>
@@ -1519,7 +1540,7 @@
         <v>80.25</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>3</v>
       </c>
@@ -1530,7 +1551,7 @@
         <v>89.27</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>3</v>
       </c>
@@ -1541,7 +1562,7 @@
         <v>105.8</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>3</v>
       </c>
@@ -1552,7 +1573,7 @@
         <v>43.9</v>
       </c>
     </row>
-    <row r="108" spans="1:3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>3</v>
       </c>
@@ -1563,7 +1584,7 @@
         <v>51.14</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>3</v>
       </c>
@@ -1574,7 +1595,7 @@
         <v>49.91</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>3</v>
       </c>
@@ -1585,7 +1606,7 @@
         <v>57.27</v>
       </c>
     </row>
-    <row r="111" spans="1:3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>3</v>
       </c>
@@ -1596,7 +1617,7 @@
         <v>47.4</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>3</v>
       </c>
@@ -1607,7 +1628,7 @@
         <v>111.57</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>3</v>
       </c>
@@ -1618,7 +1639,7 @@
         <v>55.08</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>3</v>
       </c>
@@ -1629,7 +1650,7 @@
         <v>71.13</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>3</v>
       </c>
@@ -1640,7 +1661,7 @@
         <v>100.33</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>3</v>
       </c>
@@ -1651,7 +1672,7 @@
         <v>73.47</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>3</v>
       </c>
@@ -1662,18 +1683,18 @@
         <v>60.34</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>3</v>
       </c>
       <c r="B118">
-        <v>2583.26</v>
+        <v>2583.2600000000002</v>
       </c>
       <c r="C118">
         <v>59.44</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>3</v>
       </c>
@@ -1681,10 +1702,10 @@
         <v>2790.47</v>
       </c>
       <c r="C119">
-        <v>72.90000000000001</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3">
+        <v>72.900000000000006</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>3</v>
       </c>
@@ -1695,7 +1716,7 @@
         <v>65.09</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>4</v>
       </c>
@@ -1706,18 +1727,18 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>4</v>
       </c>
       <c r="B122">
-        <v>38.23</v>
+        <v>38.229999999999997</v>
       </c>
       <c r="C122">
         <v>0.99</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>4</v>
       </c>
@@ -1725,10 +1746,10 @@
         <v>38.5</v>
       </c>
       <c r="C123">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>4</v>
       </c>
@@ -1739,18 +1760,18 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>4</v>
       </c>
       <c r="B125">
-        <v>40.66</v>
+        <v>40.659999999999997</v>
       </c>
       <c r="C125">
         <v>1.6</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>4</v>
       </c>
@@ -1761,7 +1782,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>4</v>
       </c>
@@ -1772,7 +1793,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>4</v>
       </c>
@@ -1783,7 +1804,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>4</v>
       </c>
@@ -1791,10 +1812,10 @@
         <v>46.47</v>
       </c>
       <c r="C129">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>4</v>
       </c>
@@ -1805,18 +1826,18 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="131" spans="1:3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>4</v>
       </c>
       <c r="B131">
-        <v>1113.4</v>
+        <v>1113.4000000000001</v>
       </c>
       <c r="C131">
         <v>24.64</v>
       </c>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>4</v>
       </c>
@@ -1827,7 +1848,7 @@
         <v>43.72</v>
       </c>
     </row>
-    <row r="133" spans="1:3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>4</v>
       </c>
@@ -1838,29 +1859,29 @@
         <v>33.64</v>
       </c>
     </row>
-    <row r="134" spans="1:3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>4</v>
       </c>
       <c r="B134">
-        <v>1071.35</v>
+        <v>1071.3499999999999</v>
       </c>
       <c r="C134">
         <v>24.88</v>
       </c>
     </row>
-    <row r="135" spans="1:3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>4</v>
       </c>
       <c r="B135">
-        <v>1043.38</v>
+        <v>1043.3800000000001</v>
       </c>
       <c r="C135">
         <v>25.94</v>
       </c>
     </row>
-    <row r="136" spans="1:3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>4</v>
       </c>
@@ -1871,18 +1892,18 @@
         <v>30.01</v>
       </c>
     </row>
-    <row r="137" spans="1:3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>4</v>
       </c>
       <c r="B137">
-        <v>1109.59</v>
+        <v>1109.5899999999999</v>
       </c>
       <c r="C137">
         <v>27.89</v>
       </c>
     </row>
-    <row r="138" spans="1:3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>4</v>
       </c>
@@ -1890,21 +1911,21 @@
         <v>1066.27</v>
       </c>
       <c r="C138">
-        <v>34.27</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3">
+        <v>34.270000000000003</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>4</v>
       </c>
       <c r="B139">
-        <v>1059.64</v>
+        <v>1059.6400000000001</v>
       </c>
       <c r="C139">
         <v>41.1</v>
       </c>
     </row>
-    <row r="140" spans="1:3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>4</v>
       </c>
@@ -1915,7 +1936,7 @@
         <v>18.77</v>
       </c>
     </row>
-    <row r="141" spans="1:3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>4</v>
       </c>
@@ -1926,40 +1947,40 @@
         <v>38.11</v>
       </c>
     </row>
-    <row r="142" spans="1:3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>4</v>
       </c>
       <c r="B142">
-        <v>1038.12</v>
+        <v>1038.1199999999999</v>
       </c>
       <c r="C142">
-        <v>37.77</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3">
+        <v>37.770000000000003</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>4</v>
       </c>
       <c r="B143">
-        <v>1101.66</v>
+        <v>1101.6600000000001</v>
       </c>
       <c r="C143">
         <v>23.42</v>
       </c>
     </row>
-    <row r="144" spans="1:3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>4</v>
       </c>
       <c r="B144">
-        <v>1190.84</v>
+        <v>1190.8399999999999</v>
       </c>
       <c r="C144">
         <v>47.01</v>
       </c>
     </row>
-    <row r="145" spans="1:3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>4</v>
       </c>
@@ -1970,7 +1991,7 @@
         <v>39.58</v>
       </c>
     </row>
-    <row r="146" spans="1:3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>4</v>
       </c>
@@ -1981,7 +2002,7 @@
         <v>35.18</v>
       </c>
     </row>
-    <row r="147" spans="1:3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>4</v>
       </c>
@@ -1992,7 +2013,7 @@
         <v>19.07</v>
       </c>
     </row>
-    <row r="148" spans="1:3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>4</v>
       </c>
@@ -2003,18 +2024,18 @@
         <v>27.27</v>
       </c>
     </row>
-    <row r="149" spans="1:3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>4</v>
       </c>
       <c r="B149">
-        <v>1103.62</v>
+        <v>1103.6199999999999</v>
       </c>
       <c r="C149">
         <v>37.72</v>
       </c>
     </row>
-    <row r="150" spans="1:3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>4</v>
       </c>
@@ -2025,18 +2046,18 @@
         <v>32.76</v>
       </c>
     </row>
-    <row r="151" spans="1:3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>4</v>
       </c>
       <c r="B151">
-        <v>1080.41</v>
+        <v>1080.4100000000001</v>
       </c>
       <c r="C151">
-        <v>18.81</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3">
+        <v>18.809999999999999</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>4</v>
       </c>
@@ -2044,10 +2065,10 @@
         <v>1094.97</v>
       </c>
       <c r="C152">
-        <v>37.59</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3">
+        <v>37.590000000000003</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>4</v>
       </c>
@@ -2058,7 +2079,7 @@
         <v>28.05</v>
       </c>
     </row>
-    <row r="154" spans="1:3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>4</v>
       </c>
@@ -2069,7 +2090,7 @@
         <v>23.13</v>
       </c>
     </row>
-    <row r="155" spans="1:3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>4</v>
       </c>
@@ -2080,18 +2101,18 @@
         <v>24.62</v>
       </c>
     </row>
-    <row r="156" spans="1:3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>4</v>
       </c>
       <c r="B156">
-        <v>1059.38</v>
+        <v>1059.3800000000001</v>
       </c>
       <c r="C156">
         <v>19.59</v>
       </c>
     </row>
-    <row r="157" spans="1:3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>4</v>
       </c>
@@ -2102,7 +2123,7 @@
         <v>26.76</v>
       </c>
     </row>
-    <row r="158" spans="1:3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>4</v>
       </c>
@@ -2113,7 +2134,7 @@
         <v>17.11</v>
       </c>
     </row>
-    <row r="159" spans="1:3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>4</v>
       </c>
@@ -2124,18 +2145,18 @@
         <v>42.3</v>
       </c>
     </row>
-    <row r="160" spans="1:3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>4</v>
       </c>
       <c r="B160">
-        <v>1043.14</v>
+        <v>1043.1400000000001</v>
       </c>
       <c r="C160">
         <v>20.11</v>
       </c>
     </row>
-    <row r="161" spans="1:3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>4</v>
       </c>
@@ -2146,18 +2167,18 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="162" spans="1:3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>4</v>
       </c>
       <c r="B162">
-        <v>1118.39</v>
+        <v>1118.3900000000001</v>
       </c>
       <c r="C162">
         <v>25.97</v>
       </c>
     </row>
-    <row r="163" spans="1:3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>4</v>
       </c>
@@ -2168,7 +2189,7 @@
         <v>28.7</v>
       </c>
     </row>
-    <row r="164" spans="1:3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>4</v>
       </c>
@@ -2179,18 +2200,18 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="165" spans="1:3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>4</v>
       </c>
       <c r="B165">
-        <v>1116.62</v>
+        <v>1116.6199999999999</v>
       </c>
       <c r="C165">
         <v>41.65</v>
       </c>
     </row>
-    <row r="166" spans="1:3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>4</v>
       </c>
@@ -2201,7 +2222,7 @@
         <v>22.73</v>
       </c>
     </row>
-    <row r="167" spans="1:3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>4</v>
       </c>
@@ -2212,18 +2233,18 @@
         <v>46.17</v>
       </c>
     </row>
-    <row r="168" spans="1:3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>4</v>
       </c>
       <c r="B168">
-        <v>985.9299999999999</v>
+        <v>985.93</v>
       </c>
       <c r="C168">
         <v>25.06</v>
       </c>
     </row>
-    <row r="169" spans="1:3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>4</v>
       </c>
@@ -2234,7 +2255,7 @@
         <v>44.28</v>
       </c>
     </row>
-    <row r="170" spans="1:3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>4</v>
       </c>
@@ -2245,7 +2266,7 @@
         <v>25.43</v>
       </c>
     </row>
-    <row r="171" spans="1:3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>4</v>
       </c>
@@ -2256,7 +2277,7 @@
         <v>19.48</v>
       </c>
     </row>
-    <row r="172" spans="1:3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>4</v>
       </c>
@@ -2267,7 +2288,7 @@
         <v>40.24</v>
       </c>
     </row>
-    <row r="173" spans="1:3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>4</v>
       </c>
@@ -2278,7 +2299,7 @@
         <v>22.35</v>
       </c>
     </row>
-    <row r="174" spans="1:3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>4</v>
       </c>
@@ -2286,10 +2307,10 @@
         <v>1126.77</v>
       </c>
       <c r="C174">
-        <v>38.12</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3">
+        <v>38.119999999999997</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>4</v>
       </c>
@@ -2300,7 +2321,7 @@
         <v>40.36</v>
       </c>
     </row>
-    <row r="176" spans="1:3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>4</v>
       </c>
@@ -2311,7 +2332,7 @@
         <v>24.45</v>
       </c>
     </row>
-    <row r="177" spans="1:3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>4</v>
       </c>
@@ -2322,18 +2343,18 @@
         <v>25.21</v>
       </c>
     </row>
-    <row r="178" spans="1:3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>4</v>
       </c>
       <c r="B178">
-        <v>1073.66</v>
+        <v>1073.6600000000001</v>
       </c>
       <c r="C178">
         <v>31.71</v>
       </c>
     </row>
-    <row r="179" spans="1:3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>4</v>
       </c>
@@ -2344,7 +2365,7 @@
         <v>65.02</v>
       </c>
     </row>
-    <row r="180" spans="1:3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>4</v>
       </c>
@@ -2355,7 +2376,7 @@
         <v>61.72</v>
       </c>
     </row>
-    <row r="181" spans="1:3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>4</v>
       </c>
@@ -2366,7 +2387,7 @@
         <v>50.89</v>
       </c>
     </row>
-    <row r="182" spans="1:3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>4</v>
       </c>
@@ -2377,7 +2398,7 @@
         <v>52.57</v>
       </c>
     </row>
-    <row r="183" spans="1:3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>4</v>
       </c>
@@ -2385,10 +2406,10 @@
         <v>1839.66</v>
       </c>
       <c r="C183">
-        <v>64.90000000000001</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3">
+        <v>64.900000000000006</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>4</v>
       </c>
@@ -2399,7 +2420,7 @@
         <v>33.89</v>
       </c>
     </row>
-    <row r="185" spans="1:3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>4</v>
       </c>
@@ -2410,7 +2431,7 @@
         <v>65.17</v>
       </c>
     </row>
-    <row r="186" spans="1:3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>4</v>
       </c>
@@ -2421,7 +2442,7 @@
         <v>63.51</v>
       </c>
     </row>
-    <row r="187" spans="1:3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>4</v>
       </c>
@@ -2432,7 +2453,7 @@
         <v>38.04</v>
       </c>
     </row>
-    <row r="188" spans="1:3">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>4</v>
       </c>
@@ -2443,7 +2464,7 @@
         <v>52.48</v>
       </c>
     </row>
-    <row r="189" spans="1:3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>4</v>
       </c>
@@ -2454,7 +2475,7 @@
         <v>58.45</v>
       </c>
     </row>
-    <row r="190" spans="1:3">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>4</v>
       </c>
@@ -2465,7 +2486,7 @@
         <v>54.23</v>
       </c>
     </row>
-    <row r="191" spans="1:3">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>4</v>
       </c>
@@ -2476,7 +2497,7 @@
         <v>32.08</v>
       </c>
     </row>
-    <row r="192" spans="1:3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>4</v>
       </c>
@@ -2487,7 +2508,7 @@
         <v>29.44</v>
       </c>
     </row>
-    <row r="193" spans="1:3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>4</v>
       </c>
@@ -2495,10 +2516,10 @@
         <v>1777.54</v>
       </c>
       <c r="C193">
-        <v>37.95</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3">
+        <v>37.950000000000003</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>4</v>
       </c>
@@ -2509,7 +2530,7 @@
         <v>31.19</v>
       </c>
     </row>
-    <row r="195" spans="1:3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>4</v>
       </c>
@@ -2520,7 +2541,7 @@
         <v>46.07</v>
       </c>
     </row>
-    <row r="196" spans="1:3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>4</v>
       </c>
@@ -2531,7 +2552,7 @@
         <v>56.64</v>
       </c>
     </row>
-    <row r="197" spans="1:3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>4</v>
       </c>
@@ -2542,7 +2563,7 @@
         <v>49.35</v>
       </c>
     </row>
-    <row r="198" spans="1:3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>4</v>
       </c>
@@ -2553,7 +2574,7 @@
         <v>65.22</v>
       </c>
     </row>
-    <row r="199" spans="1:3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>4</v>
       </c>
@@ -2564,7 +2585,7 @@
         <v>49.34</v>
       </c>
     </row>
-    <row r="200" spans="1:3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>4</v>
       </c>
@@ -2575,7 +2596,7 @@
         <v>46.31</v>
       </c>
     </row>
-    <row r="201" spans="1:3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>4</v>
       </c>
@@ -2586,7 +2607,7 @@
         <v>33.43</v>
       </c>
     </row>
-    <row r="202" spans="1:3">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>4</v>
       </c>
@@ -2597,7 +2618,7 @@
         <v>70.38</v>
       </c>
     </row>
-    <row r="203" spans="1:3">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>4</v>
       </c>
@@ -2608,7 +2629,7 @@
         <v>55.76</v>
       </c>
     </row>
-    <row r="204" spans="1:3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>4</v>
       </c>
@@ -2619,7 +2640,7 @@
         <v>68.41</v>
       </c>
     </row>
-    <row r="205" spans="1:3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>4</v>
       </c>
@@ -2630,7 +2651,7 @@
         <v>65.52</v>
       </c>
     </row>
-    <row r="206" spans="1:3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>4</v>
       </c>
@@ -2641,7 +2662,7 @@
         <v>29.44</v>
       </c>
     </row>
-    <row r="207" spans="1:3">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>4</v>
       </c>
@@ -2652,7 +2673,7 @@
         <v>53.7</v>
       </c>
     </row>
-    <row r="208" spans="1:3">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>4</v>
       </c>
@@ -2663,7 +2684,7 @@
         <v>44.96</v>
       </c>
     </row>
-    <row r="209" spans="1:3">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>4</v>
       </c>
@@ -2674,7 +2695,7 @@
         <v>59.88</v>
       </c>
     </row>
-    <row r="210" spans="1:3">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>4</v>
       </c>
@@ -2685,7 +2706,7 @@
         <v>29.35</v>
       </c>
     </row>
-    <row r="211" spans="1:3">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>4</v>
       </c>
@@ -2696,7 +2717,7 @@
         <v>56.7</v>
       </c>
     </row>
-    <row r="212" spans="1:3">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>4</v>
       </c>
@@ -2707,7 +2728,7 @@
         <v>52.62</v>
       </c>
     </row>
-    <row r="213" spans="1:3">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>4</v>
       </c>
@@ -2718,7 +2739,7 @@
         <v>41.8</v>
       </c>
     </row>
-    <row r="214" spans="1:3">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
         <v>4</v>
       </c>
@@ -2729,7 +2750,7 @@
         <v>33.08</v>
       </c>
     </row>
-    <row r="215" spans="1:3">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>4</v>
       </c>
@@ -2740,7 +2761,7 @@
         <v>54.83</v>
       </c>
     </row>
-    <row r="216" spans="1:3">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
         <v>4</v>
       </c>
@@ -2751,7 +2772,7 @@
         <v>29.33</v>
       </c>
     </row>
-    <row r="217" spans="1:3">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>4</v>
       </c>
@@ -2762,7 +2783,7 @@
         <v>41.51</v>
       </c>
     </row>
-    <row r="218" spans="1:3">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>4</v>
       </c>
@@ -2773,7 +2794,7 @@
         <v>28.53</v>
       </c>
     </row>
-    <row r="219" spans="1:3">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>4</v>
       </c>
@@ -2784,7 +2805,7 @@
         <v>62.8</v>
       </c>
     </row>
-    <row r="220" spans="1:3">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>4</v>
       </c>
@@ -2795,7 +2816,7 @@
         <v>58.08</v>
       </c>
     </row>
-    <row r="221" spans="1:3">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>4</v>
       </c>
@@ -2806,18 +2827,18 @@
         <v>82.91</v>
       </c>
     </row>
-    <row r="222" spans="1:3">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>4</v>
       </c>
       <c r="B222">
-        <v>2550.32</v>
+        <v>2550.3200000000002</v>
       </c>
       <c r="C222">
         <v>82.67</v>
       </c>
     </row>
-    <row r="223" spans="1:3">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>4</v>
       </c>
@@ -2825,10 +2846,10 @@
         <v>2688.99</v>
       </c>
       <c r="C223">
-        <v>88.70999999999999</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3">
+        <v>88.71</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>4</v>
       </c>
@@ -2839,7 +2860,7 @@
         <v>67.63</v>
       </c>
     </row>
-    <row r="225" spans="1:3">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>4</v>
       </c>
@@ -2850,7 +2871,7 @@
         <v>94.75</v>
       </c>
     </row>
-    <row r="226" spans="1:3">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>4</v>
       </c>
@@ -2861,18 +2882,18 @@
         <v>88.83</v>
       </c>
     </row>
-    <row r="227" spans="1:3">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
         <v>4</v>
       </c>
       <c r="B227">
-        <v>2563.43</v>
+        <v>2563.4299999999998</v>
       </c>
       <c r="C227">
         <v>73.89</v>
       </c>
     </row>
-    <row r="228" spans="1:3">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
         <v>4</v>
       </c>
@@ -2880,10 +2901,10 @@
         <v>2710.14</v>
       </c>
       <c r="C228">
-        <v>94.04000000000001</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3">
+        <v>94.04</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
         <v>4</v>
       </c>
@@ -2894,7 +2915,7 @@
         <v>105.82</v>
       </c>
     </row>
-    <row r="230" spans="1:3">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>4</v>
       </c>
@@ -2905,7 +2926,7 @@
         <v>72.33</v>
       </c>
     </row>
-    <row r="231" spans="1:3">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
         <v>4</v>
       </c>
@@ -2916,7 +2937,7 @@
         <v>106.97</v>
       </c>
     </row>
-    <row r="232" spans="1:3">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
         <v>4</v>
       </c>
@@ -2924,10 +2945,10 @@
         <v>2667.68</v>
       </c>
       <c r="C232">
-        <v>82.59999999999999</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3">
+        <v>82.6</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
         <v>4</v>
       </c>
@@ -2938,7 +2959,7 @@
         <v>65.14</v>
       </c>
     </row>
-    <row r="234" spans="1:3">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
         <v>4</v>
       </c>
@@ -2946,10 +2967,10 @@
         <v>2681.33</v>
       </c>
       <c r="C234">
-        <v>73.56999999999999</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3">
+        <v>73.569999999999993</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
         <v>4</v>
       </c>
@@ -2960,7 +2981,7 @@
         <v>85.33</v>
       </c>
     </row>
-    <row r="236" spans="1:3">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
         <v>4</v>
       </c>
@@ -2971,7 +2992,7 @@
         <v>63.81</v>
       </c>
     </row>
-    <row r="237" spans="1:3">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
         <v>4</v>
       </c>
@@ -2982,7 +3003,7 @@
         <v>99.72</v>
       </c>
     </row>
-    <row r="238" spans="1:3">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
         <v>4</v>
       </c>
@@ -2990,10 +3011,10 @@
         <v>2743.1</v>
       </c>
       <c r="C238">
-        <v>69.29000000000001</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3">
+        <v>69.290000000000006</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
         <v>5</v>
       </c>
@@ -3001,10 +3022,10 @@
         <v>36.47</v>
       </c>
       <c r="C239">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
         <v>5</v>
       </c>
@@ -3015,7 +3036,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="241" spans="1:3">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
         <v>5</v>
       </c>
@@ -3026,29 +3047,29 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="242" spans="1:3">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
         <v>5</v>
       </c>
       <c r="B242">
-        <v>34.84</v>
+        <v>34.840000000000003</v>
       </c>
       <c r="C242">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3">
+        <v>1.1200000000000001</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
         <v>5</v>
       </c>
       <c r="B243">
-        <v>1067.36</v>
+        <v>1067.3599999999999</v>
       </c>
       <c r="C243">
-        <v>35.37</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3">
+        <v>35.369999999999997</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
         <v>5</v>
       </c>
@@ -3056,10 +3077,10 @@
         <v>1159.75</v>
       </c>
       <c r="C244">
-        <v>39.62</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3">
+        <v>39.619999999999997</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
         <v>5</v>
       </c>
@@ -3067,10 +3088,10 @@
         <v>1098.33</v>
       </c>
       <c r="C245">
-        <v>33.05</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3">
+        <v>33.049999999999997</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
         <v>5</v>
       </c>
@@ -3081,7 +3102,7 @@
         <v>27.69</v>
       </c>
     </row>
-    <row r="247" spans="1:3">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
         <v>5</v>
       </c>
@@ -3092,7 +3113,7 @@
         <v>39.76</v>
       </c>
     </row>
-    <row r="248" spans="1:3">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
         <v>5</v>
       </c>
@@ -3103,7 +3124,7 @@
         <v>21.59</v>
       </c>
     </row>
-    <row r="249" spans="1:3">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
         <v>5</v>
       </c>
@@ -3114,29 +3135,29 @@
         <v>22.56</v>
       </c>
     </row>
-    <row r="250" spans="1:3">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
         <v>5</v>
       </c>
       <c r="B250">
-        <v>1082.87</v>
+        <v>1082.8699999999999</v>
       </c>
       <c r="C250">
         <v>25.45</v>
       </c>
     </row>
-    <row r="251" spans="1:3">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
         <v>5</v>
       </c>
       <c r="B251">
-        <v>1095.1</v>
+        <v>1095.0999999999999</v>
       </c>
       <c r="C251">
         <v>23.69</v>
       </c>
     </row>
-    <row r="252" spans="1:3">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
         <v>5</v>
       </c>
@@ -3147,18 +3168,18 @@
         <v>43.72</v>
       </c>
     </row>
-    <row r="253" spans="1:3">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
         <v>5</v>
       </c>
       <c r="B253">
-        <v>1088.39</v>
+        <v>1088.3900000000001</v>
       </c>
       <c r="C253">
         <v>31.27</v>
       </c>
     </row>
-    <row r="254" spans="1:3">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
         <v>5</v>
       </c>
@@ -3169,7 +3190,7 @@
         <v>43.98</v>
       </c>
     </row>
-    <row r="255" spans="1:3">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
         <v>5</v>
       </c>
@@ -3180,7 +3201,7 @@
         <v>31.27</v>
       </c>
     </row>
-    <row r="256" spans="1:3">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
         <v>5</v>
       </c>
@@ -3191,7 +3212,7 @@
         <v>23.75</v>
       </c>
     </row>
-    <row r="257" spans="1:3">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
         <v>5</v>
       </c>
@@ -3202,18 +3223,18 @@
         <v>40.57</v>
       </c>
     </row>
-    <row r="258" spans="1:3">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
         <v>5</v>
       </c>
       <c r="B258">
-        <v>1114.85</v>
+        <v>1114.8499999999999</v>
       </c>
       <c r="C258">
         <v>41.44</v>
       </c>
     </row>
-    <row r="259" spans="1:3">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
         <v>5</v>
       </c>
@@ -3224,7 +3245,7 @@
         <v>19.78</v>
       </c>
     </row>
-    <row r="260" spans="1:3">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
         <v>5</v>
       </c>
@@ -3235,40 +3256,40 @@
         <v>39.92</v>
       </c>
     </row>
-    <row r="261" spans="1:3">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
         <v>5</v>
       </c>
       <c r="B261">
-        <v>1085.14</v>
+        <v>1085.1400000000001</v>
       </c>
       <c r="C261">
         <v>32.17</v>
       </c>
     </row>
-    <row r="262" spans="1:3">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
         <v>5</v>
       </c>
       <c r="B262">
-        <v>1091.37</v>
+        <v>1091.3699999999999</v>
       </c>
       <c r="C262">
         <v>22.16</v>
       </c>
     </row>
-    <row r="263" spans="1:3">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
         <v>5</v>
       </c>
       <c r="B263">
-        <v>1052.6</v>
+        <v>1052.5999999999999</v>
       </c>
       <c r="C263">
         <v>25.36</v>
       </c>
     </row>
-    <row r="264" spans="1:3">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
         <v>5</v>
       </c>
@@ -3276,10 +3297,10 @@
         <v>1060.81</v>
       </c>
       <c r="C264">
-        <v>35.66</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3">
+        <v>35.659999999999997</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
         <v>5</v>
       </c>
@@ -3290,7 +3311,7 @@
         <v>22.79</v>
       </c>
     </row>
-    <row r="266" spans="1:3">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>5</v>
       </c>
@@ -3301,29 +3322,29 @@
         <v>34.53</v>
       </c>
     </row>
-    <row r="267" spans="1:3">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
         <v>5</v>
       </c>
       <c r="B267">
-        <v>1120.13</v>
+        <v>1120.1300000000001</v>
       </c>
       <c r="C267">
         <v>32.25</v>
       </c>
     </row>
-    <row r="268" spans="1:3">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
         <v>5</v>
       </c>
       <c r="B268">
-        <v>1138.36</v>
+        <v>1138.3599999999999</v>
       </c>
       <c r="C268">
         <v>32.71</v>
       </c>
     </row>
-    <row r="269" spans="1:3">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
         <v>5</v>
       </c>
@@ -3334,18 +3355,18 @@
         <v>22.79</v>
       </c>
     </row>
-    <row r="270" spans="1:3">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
         <v>5</v>
       </c>
       <c r="B270">
-        <v>1091.14</v>
+        <v>1091.1400000000001</v>
       </c>
       <c r="C270">
         <v>39.07</v>
       </c>
     </row>
-    <row r="271" spans="1:3">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
         <v>5</v>
       </c>
@@ -3353,10 +3374,10 @@
         <v>1123.46</v>
       </c>
       <c r="C271">
-        <v>32.55</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3">
+        <v>32.549999999999997</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
         <v>5</v>
       </c>
@@ -3367,7 +3388,7 @@
         <v>36.24</v>
       </c>
     </row>
-    <row r="273" spans="1:3">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
         <v>5</v>
       </c>
@@ -3375,10 +3396,10 @@
         <v>1085.98</v>
       </c>
       <c r="C273">
-        <v>33.73</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3">
+        <v>33.729999999999997</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
         <v>5</v>
       </c>
@@ -3389,7 +3410,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="275" spans="1:3">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
         <v>5</v>
       </c>
@@ -3397,21 +3418,21 @@
         <v>1141.43</v>
       </c>
       <c r="C275">
-        <v>38.45</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3">
+        <v>38.450000000000003</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
         <v>5</v>
       </c>
       <c r="B276">
-        <v>1099.38</v>
+        <v>1099.3800000000001</v>
       </c>
       <c r="C276">
         <v>28.07</v>
       </c>
     </row>
-    <row r="277" spans="1:3">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
         <v>5</v>
       </c>
@@ -3422,7 +3443,7 @@
         <v>41.03</v>
       </c>
     </row>
-    <row r="278" spans="1:3">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
         <v>5</v>
       </c>
@@ -3433,7 +3454,7 @@
         <v>30.2</v>
       </c>
     </row>
-    <row r="279" spans="1:3">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
         <v>5</v>
       </c>
@@ -3444,7 +3465,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="280" spans="1:3">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
         <v>5</v>
       </c>
@@ -3455,7 +3476,7 @@
         <v>29.37</v>
       </c>
     </row>
-    <row r="281" spans="1:3">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
         <v>5</v>
       </c>
@@ -3466,7 +3487,7 @@
         <v>27.65</v>
       </c>
     </row>
-    <row r="282" spans="1:3">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
         <v>5</v>
       </c>
@@ -3477,7 +3498,7 @@
         <v>42.12</v>
       </c>
     </row>
-    <row r="283" spans="1:3">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
         <v>5</v>
       </c>
@@ -3488,7 +3509,7 @@
         <v>26.64</v>
       </c>
     </row>
-    <row r="284" spans="1:3">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
         <v>5</v>
       </c>
@@ -3499,18 +3520,18 @@
         <v>37.97</v>
       </c>
     </row>
-    <row r="285" spans="1:3">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
         <v>5</v>
       </c>
       <c r="B285">
-        <v>1104.63</v>
+        <v>1104.6300000000001</v>
       </c>
       <c r="C285">
-        <v>18.35</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3">
+        <v>18.350000000000001</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
         <v>5</v>
       </c>
@@ -3521,7 +3542,7 @@
         <v>21.87</v>
       </c>
     </row>
-    <row r="287" spans="1:3">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
         <v>5</v>
       </c>
@@ -3532,7 +3553,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="288" spans="1:3">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
         <v>5</v>
       </c>
@@ -3540,21 +3561,21 @@
         <v>1149.56</v>
       </c>
       <c r="C288">
-        <v>38.84</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3">
+        <v>38.840000000000003</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
         <v>5</v>
       </c>
       <c r="B289">
-        <v>1111.41</v>
+        <v>1111.4100000000001</v>
       </c>
       <c r="C289">
-        <v>33.84</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3">
+        <v>33.840000000000003</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
         <v>5</v>
       </c>
@@ -3565,7 +3586,7 @@
         <v>27.76</v>
       </c>
     </row>
-    <row r="291" spans="1:3">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
         <v>5</v>
       </c>
@@ -3576,29 +3597,29 @@
         <v>28.47</v>
       </c>
     </row>
-    <row r="292" spans="1:3">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
         <v>5</v>
       </c>
       <c r="B292">
-        <v>1028.62</v>
+        <v>1028.6199999999999</v>
       </c>
       <c r="C292">
-        <v>37.23</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3">
+        <v>37.229999999999997</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
         <v>5</v>
       </c>
       <c r="B293">
-        <v>1067.38</v>
+        <v>1067.3800000000001</v>
       </c>
       <c r="C293">
         <v>22.64</v>
       </c>
     </row>
-    <row r="294" spans="1:3">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
         <v>5</v>
       </c>
@@ -3606,10 +3627,10 @@
         <v>1163.08</v>
       </c>
       <c r="C294">
-        <v>40.59</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3">
+        <v>40.590000000000003</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
         <v>5</v>
       </c>
@@ -3620,7 +3641,7 @@
         <v>26.31</v>
       </c>
     </row>
-    <row r="296" spans="1:3">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
         <v>5</v>
       </c>
@@ -3631,7 +3652,7 @@
         <v>37.97</v>
       </c>
     </row>
-    <row r="297" spans="1:3">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
         <v>5</v>
       </c>
@@ -3642,7 +3663,7 @@
         <v>60.37</v>
       </c>
     </row>
-    <row r="298" spans="1:3">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
         <v>5</v>
       </c>
@@ -3653,7 +3674,7 @@
         <v>46.03</v>
       </c>
     </row>
-    <row r="299" spans="1:3">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
         <v>5</v>
       </c>
@@ -3664,7 +3685,7 @@
         <v>35.19</v>
       </c>
     </row>
-    <row r="300" spans="1:3">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
         <v>5</v>
       </c>
@@ -3675,7 +3696,7 @@
         <v>34.57</v>
       </c>
     </row>
-    <row r="301" spans="1:3">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
         <v>5</v>
       </c>
@@ -3686,7 +3707,7 @@
         <v>36.64</v>
       </c>
     </row>
-    <row r="302" spans="1:3">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
         <v>5</v>
       </c>
@@ -3697,7 +3718,7 @@
         <v>31.29</v>
       </c>
     </row>
-    <row r="303" spans="1:3">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
         <v>5</v>
       </c>
@@ -3708,7 +3729,7 @@
         <v>43.12</v>
       </c>
     </row>
-    <row r="304" spans="1:3">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
         <v>5</v>
       </c>
@@ -3719,7 +3740,7 @@
         <v>51.37</v>
       </c>
     </row>
-    <row r="305" spans="1:3">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
         <v>5</v>
       </c>
@@ -3730,7 +3751,7 @@
         <v>43.46</v>
       </c>
     </row>
-    <row r="306" spans="1:3">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A306" t="s">
         <v>5</v>
       </c>
@@ -3741,7 +3762,7 @@
         <v>64.97</v>
       </c>
     </row>
-    <row r="307" spans="1:3">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
         <v>5</v>
       </c>
@@ -3752,7 +3773,7 @@
         <v>62.26</v>
       </c>
     </row>
-    <row r="308" spans="1:3">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A308" t="s">
         <v>5</v>
       </c>
@@ -3763,7 +3784,7 @@
         <v>57.71</v>
       </c>
     </row>
-    <row r="309" spans="1:3">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A309" t="s">
         <v>5</v>
       </c>
@@ -3774,7 +3795,7 @@
         <v>61.08</v>
       </c>
     </row>
-    <row r="310" spans="1:3">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A310" t="s">
         <v>5</v>
       </c>
@@ -3785,7 +3806,7 @@
         <v>39.42</v>
       </c>
     </row>
-    <row r="311" spans="1:3">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A311" t="s">
         <v>5</v>
       </c>
@@ -3796,7 +3817,7 @@
         <v>59.73</v>
       </c>
     </row>
-    <row r="312" spans="1:3">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A312" t="s">
         <v>5</v>
       </c>
@@ -3807,7 +3828,7 @@
         <v>30.67</v>
       </c>
     </row>
-    <row r="313" spans="1:3">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
         <v>5</v>
       </c>
@@ -3818,7 +3839,7 @@
         <v>28.03</v>
       </c>
     </row>
-    <row r="314" spans="1:3">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A314" t="s">
         <v>5</v>
       </c>
@@ -3829,7 +3850,7 @@
         <v>28.98</v>
       </c>
     </row>
-    <row r="315" spans="1:3">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A315" t="s">
         <v>5</v>
       </c>
@@ -3840,7 +3861,7 @@
         <v>38.61</v>
       </c>
     </row>
-    <row r="316" spans="1:3">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
         <v>5</v>
       </c>
@@ -3851,7 +3872,7 @@
         <v>56.82</v>
       </c>
     </row>
-    <row r="317" spans="1:3">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A317" t="s">
         <v>5</v>
       </c>
@@ -3862,7 +3883,7 @@
         <v>29.22</v>
       </c>
     </row>
-    <row r="318" spans="1:3">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A318" t="s">
         <v>5</v>
       </c>
@@ -3873,7 +3894,7 @@
         <v>43.18</v>
       </c>
     </row>
-    <row r="319" spans="1:3">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A319" t="s">
         <v>5</v>
       </c>
@@ -3884,7 +3905,7 @@
         <v>52.34</v>
       </c>
     </row>
-    <row r="320" spans="1:3">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A320" t="s">
         <v>5</v>
       </c>
@@ -3895,7 +3916,7 @@
         <v>60.93</v>
       </c>
     </row>
-    <row r="321" spans="1:3">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
         <v>5</v>
       </c>
@@ -3906,7 +3927,7 @@
         <v>50.62</v>
       </c>
     </row>
-    <row r="322" spans="1:3">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
         <v>5</v>
       </c>
@@ -3914,10 +3935,10 @@
         <v>1676.43</v>
       </c>
       <c r="C322">
-        <v>36.7</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3">
+        <v>36.700000000000003</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A323" t="s">
         <v>5</v>
       </c>
@@ -3928,7 +3949,7 @@
         <v>30.43</v>
       </c>
     </row>
-    <row r="324" spans="1:3">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A324" t="s">
         <v>5</v>
       </c>
@@ -3939,7 +3960,7 @@
         <v>46.05</v>
       </c>
     </row>
-    <row r="325" spans="1:3">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
         <v>5</v>
       </c>
@@ -3950,7 +3971,7 @@
         <v>57.32</v>
       </c>
     </row>
-    <row r="326" spans="1:3">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A326" t="s">
         <v>5</v>
       </c>
@@ -3961,7 +3982,7 @@
         <v>60.28</v>
       </c>
     </row>
-    <row r="327" spans="1:3">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A327" t="s">
         <v>5</v>
       </c>
@@ -3972,7 +3993,7 @@
         <v>50.77</v>
       </c>
     </row>
-    <row r="328" spans="1:3">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A328" t="s">
         <v>5</v>
       </c>
@@ -3983,7 +4004,7 @@
         <v>33.57</v>
       </c>
     </row>
-    <row r="329" spans="1:3">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
         <v>5</v>
       </c>
@@ -3994,7 +4015,7 @@
         <v>30.86</v>
       </c>
     </row>
-    <row r="330" spans="1:3">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A330" t="s">
         <v>5</v>
       </c>
@@ -4005,7 +4026,7 @@
         <v>29.08</v>
       </c>
     </row>
-    <row r="331" spans="1:3">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
         <v>5</v>
       </c>
@@ -4016,7 +4037,7 @@
         <v>41.48</v>
       </c>
     </row>
-    <row r="332" spans="1:3">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A332" t="s">
         <v>5</v>
       </c>
@@ -4027,7 +4048,7 @@
         <v>50.32</v>
       </c>
     </row>
-    <row r="333" spans="1:3">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A333" t="s">
         <v>5</v>
       </c>
@@ -4038,7 +4059,7 @@
         <v>32.68</v>
       </c>
     </row>
-    <row r="334" spans="1:3">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
         <v>5</v>
       </c>
@@ -4049,7 +4070,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="335" spans="1:3">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A335" t="s">
         <v>5</v>
       </c>
@@ -4060,7 +4081,7 @@
         <v>63.16</v>
       </c>
     </row>
-    <row r="336" spans="1:3">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A336" t="s">
         <v>5</v>
       </c>
@@ -4071,7 +4092,7 @@
         <v>90.47</v>
       </c>
     </row>
-    <row r="337" spans="1:3">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
         <v>5</v>
       </c>
@@ -4079,21 +4100,21 @@
         <v>2749.23</v>
       </c>
       <c r="C337">
-        <v>78.98999999999999</v>
-      </c>
-    </row>
-    <row r="338" spans="1:3">
+        <v>78.989999999999995</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A338" t="s">
         <v>5</v>
       </c>
       <c r="B338">
-        <v>2580.22</v>
+        <v>2580.2199999999998</v>
       </c>
       <c r="C338">
         <v>88.8</v>
       </c>
     </row>
-    <row r="339" spans="1:3">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
         <v>5</v>
       </c>
@@ -4104,7 +4125,7 @@
         <v>52.63</v>
       </c>
     </row>
-    <row r="340" spans="1:3">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
         <v>5</v>
       </c>
@@ -4115,18 +4136,18 @@
         <v>80.75</v>
       </c>
     </row>
-    <row r="341" spans="1:3">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A341" t="s">
         <v>5</v>
       </c>
       <c r="B341">
-        <v>2594.45</v>
+        <v>2594.4499999999998</v>
       </c>
       <c r="C341">
         <v>96.73</v>
       </c>
     </row>
-    <row r="342" spans="1:3">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A342" t="s">
         <v>5</v>
       </c>
@@ -4137,29 +4158,29 @@
         <v>45.65</v>
       </c>
     </row>
-    <row r="343" spans="1:3">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
         <v>5</v>
       </c>
       <c r="B343">
-        <v>2591.53</v>
+        <v>2591.5300000000002</v>
       </c>
       <c r="C343">
         <v>99.5</v>
       </c>
     </row>
-    <row r="344" spans="1:3">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A344" t="s">
         <v>5</v>
       </c>
       <c r="B344">
-        <v>2543.68</v>
+        <v>2543.6799999999998</v>
       </c>
       <c r="C344">
         <v>76.8</v>
       </c>
     </row>
-    <row r="345" spans="1:3">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
         <v>5</v>
       </c>
@@ -4170,7 +4191,7 @@
         <v>111.41</v>
       </c>
     </row>
-    <row r="346" spans="1:3">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A346" t="s">
         <v>5</v>
       </c>
@@ -4181,7 +4202,7 @@
         <v>58.28</v>
       </c>
     </row>
-    <row r="347" spans="1:3">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A347" t="s">
         <v>5</v>
       </c>
@@ -4189,10 +4210,10 @@
         <v>2668.31</v>
       </c>
       <c r="C347">
-        <v>74.04000000000001</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3">
+        <v>74.040000000000006</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A348" t="s">
         <v>5</v>
       </c>
@@ -4203,7 +4224,7 @@
         <v>90.12</v>
       </c>
     </row>
-    <row r="349" spans="1:3">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
         <v>5</v>
       </c>
@@ -4214,7 +4235,7 @@
         <v>80.48</v>
       </c>
     </row>
-    <row r="350" spans="1:3">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A350" t="s">
         <v>5</v>
       </c>
@@ -4222,10 +4243,10 @@
         <v>2642.75</v>
       </c>
       <c r="C350">
-        <v>81.68000000000001</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3">
+        <v>81.680000000000007</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A351" t="s">
         <v>5</v>
       </c>
@@ -4236,7 +4257,7 @@
         <v>97.72</v>
       </c>
     </row>
-    <row r="352" spans="1:3">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
         <v>5</v>
       </c>
@@ -4247,7 +4268,7 @@
         <v>54.23</v>
       </c>
     </row>
-    <row r="353" spans="1:3">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
         <v>5</v>
       </c>
@@ -4258,7 +4279,7 @@
         <v>85.62</v>
       </c>
     </row>
-    <row r="354" spans="1:3">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A354" t="s">
         <v>5</v>
       </c>
@@ -4266,10 +4287,10 @@
         <v>2704.96</v>
       </c>
       <c r="C354">
-        <v>72.18000000000001</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3">
+        <v>72.180000000000007</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A355" t="s">
         <v>5</v>
       </c>
@@ -4280,7 +4301,7 @@
         <v>102.41</v>
       </c>
     </row>
-    <row r="356" spans="1:3">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A356" t="s">
         <v>5</v>
       </c>
@@ -4291,7 +4312,7 @@
         <v>110.85</v>
       </c>
     </row>
-    <row r="357" spans="1:3">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A357" t="s">
         <v>5</v>
       </c>
@@ -4302,7 +4323,7 @@
         <v>69.84</v>
       </c>
     </row>
-    <row r="358" spans="1:3">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
         <v>6</v>
       </c>
@@ -4313,29 +4334,29 @@
         <v>25.66</v>
       </c>
     </row>
-    <row r="359" spans="1:3">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A359" t="s">
         <v>6</v>
       </c>
       <c r="B359">
-        <v>1118.11</v>
+        <v>1118.1099999999999</v>
       </c>
       <c r="C359">
         <v>42.06</v>
       </c>
     </row>
-    <row r="360" spans="1:3">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A360" t="s">
         <v>6</v>
       </c>
       <c r="B360">
-        <v>1067.13</v>
+        <v>1067.1300000000001</v>
       </c>
       <c r="C360">
         <v>41.18</v>
       </c>
     </row>
-    <row r="361" spans="1:3">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
         <v>6</v>
       </c>
@@ -4346,7 +4367,7 @@
         <v>37.94</v>
       </c>
     </row>
-    <row r="362" spans="1:3">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A362" t="s">
         <v>6</v>
       </c>
@@ -4357,7 +4378,7 @@
         <v>41.13</v>
       </c>
     </row>
-    <row r="363" spans="1:3">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A363" t="s">
         <v>6</v>
       </c>
@@ -4368,7 +4389,7 @@
         <v>44.08</v>
       </c>
     </row>
-    <row r="364" spans="1:3">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A364" t="s">
         <v>6</v>
       </c>
@@ -4379,18 +4400,18 @@
         <v>29.17</v>
       </c>
     </row>
-    <row r="365" spans="1:3">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A365" t="s">
         <v>6</v>
       </c>
       <c r="B365">
-        <v>1080.85</v>
+        <v>1080.8499999999999</v>
       </c>
       <c r="C365">
         <v>26.62</v>
       </c>
     </row>
-    <row r="366" spans="1:3">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A366" t="s">
         <v>6</v>
       </c>
@@ -4401,7 +4422,7 @@
         <v>16.86</v>
       </c>
     </row>
-    <row r="367" spans="1:3">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
         <v>6</v>
       </c>
@@ -4412,18 +4433,18 @@
         <v>27.72</v>
       </c>
     </row>
-    <row r="368" spans="1:3">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A368" t="s">
         <v>6</v>
       </c>
       <c r="B368">
-        <v>1154.14</v>
+        <v>1154.1400000000001</v>
       </c>
       <c r="C368">
         <v>24.48</v>
       </c>
     </row>
-    <row r="369" spans="1:3">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
         <v>6</v>
       </c>
@@ -4434,7 +4455,7 @@
         <v>35.22</v>
       </c>
     </row>
-    <row r="370" spans="1:3">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
         <v>6</v>
       </c>
@@ -4445,7 +4466,7 @@
         <v>32.32</v>
       </c>
     </row>
-    <row r="371" spans="1:3">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A371" t="s">
         <v>6</v>
       </c>
@@ -4453,21 +4474,21 @@
         <v>1030.19</v>
       </c>
       <c r="C371">
-        <v>39.63</v>
-      </c>
-    </row>
-    <row r="372" spans="1:3">
+        <v>39.630000000000003</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A372" t="s">
         <v>6</v>
       </c>
       <c r="B372">
-        <v>1111.09</v>
+        <v>1111.0899999999999</v>
       </c>
       <c r="C372">
-        <v>36.16</v>
-      </c>
-    </row>
-    <row r="373" spans="1:3">
+        <v>36.159999999999997</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A373" t="s">
         <v>6</v>
       </c>
@@ -4478,18 +4499,18 @@
         <v>24.06</v>
       </c>
     </row>
-    <row r="374" spans="1:3">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A374" t="s">
         <v>6</v>
       </c>
       <c r="B374">
-        <v>1031.59</v>
+        <v>1031.5899999999999</v>
       </c>
       <c r="C374">
         <v>25.77</v>
       </c>
     </row>
-    <row r="375" spans="1:3">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A375" t="s">
         <v>6</v>
       </c>
@@ -4500,7 +4521,7 @@
         <v>31.24</v>
       </c>
     </row>
-    <row r="376" spans="1:3">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
         <v>6</v>
       </c>
@@ -4511,7 +4532,7 @@
         <v>31.67</v>
       </c>
     </row>
-    <row r="377" spans="1:3">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A377" t="s">
         <v>6</v>
       </c>
@@ -4522,18 +4543,18 @@
         <v>43.17</v>
       </c>
     </row>
-    <row r="378" spans="1:3">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A378" t="s">
         <v>6</v>
       </c>
       <c r="B378">
-        <v>1056.13</v>
+        <v>1056.1300000000001</v>
       </c>
       <c r="C378">
         <v>32.94</v>
       </c>
     </row>
-    <row r="379" spans="1:3">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
         <v>6</v>
       </c>
@@ -4544,7 +4565,7 @@
         <v>27.71</v>
       </c>
     </row>
-    <row r="380" spans="1:3">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A380" t="s">
         <v>6</v>
       </c>
@@ -4555,7 +4576,7 @@
         <v>24.94</v>
       </c>
     </row>
-    <row r="381" spans="1:3">
+    <row r="381" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A381" t="s">
         <v>6</v>
       </c>
@@ -4563,21 +4584,21 @@
         <v>1079.74</v>
       </c>
       <c r="C381">
-        <v>32.2</v>
-      </c>
-    </row>
-    <row r="382" spans="1:3">
+        <v>32.200000000000003</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A382" t="s">
         <v>6</v>
       </c>
       <c r="B382">
-        <v>1061.65</v>
+        <v>1061.6500000000001</v>
       </c>
       <c r="C382">
         <v>19.16</v>
       </c>
     </row>
-    <row r="383" spans="1:3">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A383" t="s">
         <v>6</v>
       </c>
@@ -4588,29 +4609,29 @@
         <v>29</v>
       </c>
     </row>
-    <row r="384" spans="1:3">
+    <row r="384" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A384" t="s">
         <v>6</v>
       </c>
       <c r="B384">
-        <v>1123.65</v>
+        <v>1123.6500000000001</v>
       </c>
       <c r="C384">
         <v>42.14</v>
       </c>
     </row>
-    <row r="385" spans="1:3">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
         <v>6</v>
       </c>
       <c r="B385">
-        <v>1072.9</v>
+        <v>1072.9000000000001</v>
       </c>
       <c r="C385">
-        <v>40.8</v>
-      </c>
-    </row>
-    <row r="386" spans="1:3">
+        <v>40.799999999999997</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A386" t="s">
         <v>6</v>
       </c>
@@ -4618,43 +4639,43 @@
         <v>1133.52</v>
       </c>
       <c r="C386">
-        <v>33.38</v>
-      </c>
-    </row>
-    <row r="387" spans="1:3">
+        <v>33.380000000000003</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A387" t="s">
         <v>6</v>
       </c>
       <c r="B387">
-        <v>1111.13</v>
+        <v>1111.1300000000001</v>
       </c>
       <c r="C387">
         <v>32.31</v>
       </c>
     </row>
-    <row r="388" spans="1:3">
+    <row r="388" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
         <v>6</v>
       </c>
       <c r="B388">
-        <v>1145.59</v>
+        <v>1145.5899999999999</v>
       </c>
       <c r="C388">
         <v>27.45</v>
       </c>
     </row>
-    <row r="389" spans="1:3">
+    <row r="389" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A389" t="s">
         <v>6</v>
       </c>
       <c r="B389">
-        <v>1121.63</v>
+        <v>1121.6300000000001</v>
       </c>
       <c r="C389">
         <v>33.79</v>
       </c>
     </row>
-    <row r="390" spans="1:3">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A390" t="s">
         <v>6</v>
       </c>
@@ -4665,7 +4686,7 @@
         <v>29.19</v>
       </c>
     </row>
-    <row r="391" spans="1:3">
+    <row r="391" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A391" t="s">
         <v>6</v>
       </c>
@@ -4676,7 +4697,7 @@
         <v>31.55</v>
       </c>
     </row>
-    <row r="392" spans="1:3">
+    <row r="392" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A392" t="s">
         <v>6</v>
       </c>
@@ -4687,7 +4708,7 @@
         <v>42.7</v>
       </c>
     </row>
-    <row r="393" spans="1:3">
+    <row r="393" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A393" t="s">
         <v>6</v>
       </c>
@@ -4695,10 +4716,10 @@
         <v>1120.51</v>
       </c>
       <c r="C393">
-        <v>38.23</v>
-      </c>
-    </row>
-    <row r="394" spans="1:3">
+        <v>38.229999999999997</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
         <v>6</v>
       </c>
@@ -4709,7 +4730,7 @@
         <v>21.08</v>
       </c>
     </row>
-    <row r="395" spans="1:3">
+    <row r="395" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A395" t="s">
         <v>6</v>
       </c>
@@ -4720,7 +4741,7 @@
         <v>22.35</v>
       </c>
     </row>
-    <row r="396" spans="1:3">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A396" t="s">
         <v>6</v>
       </c>
@@ -4731,29 +4752,29 @@
         <v>34.64</v>
       </c>
     </row>
-    <row r="397" spans="1:3">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
         <v>6</v>
       </c>
       <c r="B397">
-        <v>1067.88</v>
+        <v>1067.8800000000001</v>
       </c>
       <c r="C397">
         <v>42.06</v>
       </c>
     </row>
-    <row r="398" spans="1:3">
+    <row r="398" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A398" t="s">
         <v>6</v>
       </c>
       <c r="B398">
-        <v>1042.59</v>
+        <v>1042.5899999999999</v>
       </c>
       <c r="C398">
         <v>31.66</v>
       </c>
     </row>
-    <row r="399" spans="1:3">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A399" t="s">
         <v>6</v>
       </c>
@@ -4764,29 +4785,29 @@
         <v>41.39</v>
       </c>
     </row>
-    <row r="400" spans="1:3">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A400" t="s">
         <v>6</v>
       </c>
       <c r="B400">
-        <v>1092.13</v>
+        <v>1092.1300000000001</v>
       </c>
       <c r="C400">
         <v>24.78</v>
       </c>
     </row>
-    <row r="401" spans="1:3">
+    <row r="401" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A401" t="s">
         <v>6</v>
       </c>
       <c r="B401">
-        <v>1062.84</v>
+        <v>1062.8399999999999</v>
       </c>
       <c r="C401">
         <v>23.21</v>
       </c>
     </row>
-    <row r="402" spans="1:3">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A402" t="s">
         <v>6</v>
       </c>
@@ -4797,18 +4818,18 @@
         <v>40.58</v>
       </c>
     </row>
-    <row r="403" spans="1:3">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
         <v>6</v>
       </c>
       <c r="B403">
-        <v>1078.1</v>
+        <v>1078.0999999999999</v>
       </c>
       <c r="C403">
-        <v>39.95</v>
-      </c>
-    </row>
-    <row r="404" spans="1:3">
+        <v>39.950000000000003</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A404" t="s">
         <v>6</v>
       </c>
@@ -4819,7 +4840,7 @@
         <v>30.81</v>
       </c>
     </row>
-    <row r="405" spans="1:3">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A405" t="s">
         <v>6</v>
       </c>
@@ -4830,18 +4851,18 @@
         <v>39.35</v>
       </c>
     </row>
-    <row r="406" spans="1:3">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
         <v>6</v>
       </c>
       <c r="B406">
-        <v>1052.4</v>
+        <v>1052.4000000000001</v>
       </c>
       <c r="C406">
         <v>33.07</v>
       </c>
     </row>
-    <row r="407" spans="1:3">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A407" t="s">
         <v>6</v>
       </c>
@@ -4852,7 +4873,7 @@
         <v>39.92</v>
       </c>
     </row>
-    <row r="408" spans="1:3">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A408" t="s">
         <v>6</v>
       </c>
@@ -4860,21 +4881,21 @@
         <v>1149.28</v>
       </c>
       <c r="C408">
-        <v>34.62</v>
-      </c>
-    </row>
-    <row r="409" spans="1:3">
+        <v>34.619999999999997</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
         <v>6</v>
       </c>
       <c r="B409">
-        <v>1129.13</v>
+        <v>1129.1300000000001</v>
       </c>
       <c r="C409">
         <v>36.58</v>
       </c>
     </row>
-    <row r="410" spans="1:3">
+    <row r="410" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A410" t="s">
         <v>6</v>
       </c>
@@ -4885,7 +4906,7 @@
         <v>43.28</v>
       </c>
     </row>
-    <row r="411" spans="1:3">
+    <row r="411" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A411" t="s">
         <v>6</v>
       </c>
@@ -4896,7 +4917,7 @@
         <v>29.93</v>
       </c>
     </row>
-    <row r="412" spans="1:3">
+    <row r="412" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
         <v>6</v>
       </c>
@@ -4907,29 +4928,29 @@
         <v>37.36</v>
       </c>
     </row>
-    <row r="413" spans="1:3">
+    <row r="413" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A413" t="s">
         <v>6</v>
       </c>
       <c r="B413">
-        <v>1119.88</v>
+        <v>1119.8800000000001</v>
       </c>
       <c r="C413">
         <v>43.73</v>
       </c>
     </row>
-    <row r="414" spans="1:3">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A414" t="s">
         <v>6</v>
       </c>
       <c r="B414">
-        <v>1049.9</v>
+        <v>1049.9000000000001</v>
       </c>
       <c r="C414">
-        <v>17.83</v>
-      </c>
-    </row>
-    <row r="415" spans="1:3">
+        <v>17.829999999999998</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
         <v>6</v>
       </c>
@@ -4940,7 +4961,7 @@
         <v>39.65</v>
       </c>
     </row>
-    <row r="416" spans="1:3">
+    <row r="416" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A416" t="s">
         <v>6</v>
       </c>
@@ -4951,7 +4972,7 @@
         <v>42.49</v>
       </c>
     </row>
-    <row r="417" spans="1:3">
+    <row r="417" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
         <v>6</v>
       </c>
@@ -4962,7 +4983,7 @@
         <v>54.38</v>
       </c>
     </row>
-    <row r="418" spans="1:3">
+    <row r="418" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A418" t="s">
         <v>6</v>
       </c>
@@ -4973,7 +4994,7 @@
         <v>43.15</v>
       </c>
     </row>
-    <row r="419" spans="1:3">
+    <row r="419" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A419" t="s">
         <v>6</v>
       </c>
@@ -4984,7 +5005,7 @@
         <v>67.73</v>
       </c>
     </row>
-    <row r="420" spans="1:3">
+    <row r="420" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A420" t="s">
         <v>6</v>
       </c>
@@ -4995,7 +5016,7 @@
         <v>36.4</v>
       </c>
     </row>
-    <row r="421" spans="1:3">
+    <row r="421" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
         <v>6</v>
       </c>
@@ -5003,10 +5024,10 @@
         <v>1696.14</v>
       </c>
       <c r="C421">
-        <v>39.59</v>
-      </c>
-    </row>
-    <row r="422" spans="1:3">
+        <v>39.590000000000003</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A422" t="s">
         <v>6</v>
       </c>
@@ -5017,7 +5038,7 @@
         <v>31.04</v>
       </c>
     </row>
-    <row r="423" spans="1:3">
+    <row r="423" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A423" t="s">
         <v>6</v>
       </c>
@@ -5028,7 +5049,7 @@
         <v>35.58</v>
       </c>
     </row>
-    <row r="424" spans="1:3">
+    <row r="424" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
         <v>6</v>
       </c>
@@ -5039,7 +5060,7 @@
         <v>52.9</v>
       </c>
     </row>
-    <row r="425" spans="1:3">
+    <row r="425" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
         <v>6</v>
       </c>
@@ -5050,7 +5071,7 @@
         <v>29.06</v>
       </c>
     </row>
-    <row r="426" spans="1:3">
+    <row r="426" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A426" t="s">
         <v>6</v>
       </c>
@@ -5061,7 +5082,7 @@
         <v>65.89</v>
       </c>
     </row>
-    <row r="427" spans="1:3">
+    <row r="427" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A427" t="s">
         <v>6</v>
       </c>
@@ -5072,7 +5093,7 @@
         <v>60.62</v>
       </c>
     </row>
-    <row r="428" spans="1:3">
+    <row r="428" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A428" t="s">
         <v>6</v>
       </c>
@@ -5080,10 +5101,10 @@
         <v>1785.25</v>
       </c>
       <c r="C428">
-        <v>32.23</v>
-      </c>
-    </row>
-    <row r="429" spans="1:3">
+        <v>32.229999999999997</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A429" t="s">
         <v>6</v>
       </c>
@@ -5094,7 +5115,7 @@
         <v>60.13</v>
       </c>
     </row>
-    <row r="430" spans="1:3">
+    <row r="430" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
         <v>6</v>
       </c>
@@ -5105,7 +5126,7 @@
         <v>32.57</v>
       </c>
     </row>
-    <row r="431" spans="1:3">
+    <row r="431" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A431" t="s">
         <v>6</v>
       </c>
@@ -5116,7 +5137,7 @@
         <v>49.03</v>
       </c>
     </row>
-    <row r="432" spans="1:3">
+    <row r="432" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A432" t="s">
         <v>6</v>
       </c>
@@ -5127,7 +5148,7 @@
         <v>37.47</v>
       </c>
     </row>
-    <row r="433" spans="1:3">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
         <v>6</v>
       </c>
@@ -5135,10 +5156,10 @@
         <v>1657.03</v>
       </c>
       <c r="C433">
-        <v>33.37</v>
-      </c>
-    </row>
-    <row r="434" spans="1:3">
+        <v>33.369999999999997</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A434" t="s">
         <v>6</v>
       </c>
@@ -5149,7 +5170,7 @@
         <v>47.27</v>
       </c>
     </row>
-    <row r="435" spans="1:3">
+    <row r="435" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A435" t="s">
         <v>6</v>
       </c>
@@ -5160,7 +5181,7 @@
         <v>64.09</v>
       </c>
     </row>
-    <row r="436" spans="1:3">
+    <row r="436" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A436" t="s">
         <v>6</v>
       </c>
@@ -5171,7 +5192,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="437" spans="1:3">
+    <row r="437" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A437" t="s">
         <v>6</v>
       </c>
@@ -5182,7 +5203,7 @@
         <v>35.33</v>
       </c>
     </row>
-    <row r="438" spans="1:3">
+    <row r="438" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A438" t="s">
         <v>6</v>
       </c>
@@ -5193,7 +5214,7 @@
         <v>47.55</v>
       </c>
     </row>
-    <row r="439" spans="1:3">
+    <row r="439" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
         <v>6</v>
       </c>
@@ -5204,7 +5225,7 @@
         <v>67.8</v>
       </c>
     </row>
-    <row r="440" spans="1:3">
+    <row r="440" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A440" t="s">
         <v>6</v>
       </c>
@@ -5215,7 +5236,7 @@
         <v>40.92</v>
       </c>
     </row>
-    <row r="441" spans="1:3">
+    <row r="441" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A441" t="s">
         <v>6</v>
       </c>
@@ -5226,7 +5247,7 @@
         <v>64.87</v>
       </c>
     </row>
-    <row r="442" spans="1:3">
+    <row r="442" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
         <v>6</v>
       </c>
@@ -5237,7 +5258,7 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="443" spans="1:3">
+    <row r="443" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A443" t="s">
         <v>6</v>
       </c>
@@ -5248,7 +5269,7 @@
         <v>46.85</v>
       </c>
     </row>
-    <row r="444" spans="1:3">
+    <row r="444" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A444" t="s">
         <v>6</v>
       </c>
@@ -5259,7 +5280,7 @@
         <v>55.86</v>
       </c>
     </row>
-    <row r="445" spans="1:3">
+    <row r="445" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A445" t="s">
         <v>6</v>
       </c>
@@ -5270,7 +5291,7 @@
         <v>34.03</v>
       </c>
     </row>
-    <row r="446" spans="1:3">
+    <row r="446" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A446" t="s">
         <v>6</v>
       </c>
@@ -5281,7 +5302,7 @@
         <v>50.13</v>
       </c>
     </row>
-    <row r="447" spans="1:3">
+    <row r="447" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A447" t="s">
         <v>6</v>
       </c>
@@ -5292,7 +5313,7 @@
         <v>28.47</v>
       </c>
     </row>
-    <row r="448" spans="1:3">
+    <row r="448" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
         <v>6</v>
       </c>
@@ -5303,7 +5324,7 @@
         <v>47.76</v>
       </c>
     </row>
-    <row r="449" spans="1:3">
+    <row r="449" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
         <v>6</v>
       </c>
@@ -5314,7 +5335,7 @@
         <v>67.47</v>
       </c>
     </row>
-    <row r="450" spans="1:3">
+    <row r="450" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A450" t="s">
         <v>6</v>
       </c>
@@ -5325,7 +5346,7 @@
         <v>30.82</v>
       </c>
     </row>
-    <row r="451" spans="1:3">
+    <row r="451" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
         <v>6</v>
       </c>
@@ -5336,7 +5357,7 @@
         <v>31.46</v>
       </c>
     </row>
-    <row r="452" spans="1:3">
+    <row r="452" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A452" t="s">
         <v>6</v>
       </c>
@@ -5347,7 +5368,7 @@
         <v>50.98</v>
       </c>
     </row>
-    <row r="453" spans="1:3">
+    <row r="453" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A453" t="s">
         <v>6</v>
       </c>
@@ -5358,7 +5379,7 @@
         <v>107.01</v>
       </c>
     </row>
-    <row r="454" spans="1:3">
+    <row r="454" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
         <v>6</v>
       </c>
@@ -5369,7 +5390,7 @@
         <v>77.97</v>
       </c>
     </row>
-    <row r="455" spans="1:3">
+    <row r="455" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A455" t="s">
         <v>6</v>
       </c>
@@ -5380,7 +5401,7 @@
         <v>104.54</v>
       </c>
     </row>
-    <row r="456" spans="1:3">
+    <row r="456" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A456" t="s">
         <v>6</v>
       </c>
@@ -5391,7 +5412,7 @@
         <v>63.16</v>
       </c>
     </row>
-    <row r="457" spans="1:3">
+    <row r="457" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
         <v>6</v>
       </c>
@@ -5402,7 +5423,7 @@
         <v>111.34</v>
       </c>
     </row>
-    <row r="458" spans="1:3">
+    <row r="458" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A458" t="s">
         <v>6</v>
       </c>
@@ -5413,7 +5434,7 @@
         <v>58.72</v>
       </c>
     </row>
-    <row r="459" spans="1:3">
+    <row r="459" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A459" t="s">
         <v>6</v>
       </c>
@@ -5424,7 +5445,7 @@
         <v>96.97</v>
       </c>
     </row>
-    <row r="460" spans="1:3">
+    <row r="460" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
         <v>6</v>
       </c>
@@ -5435,7 +5456,7 @@
         <v>65.12</v>
       </c>
     </row>
-    <row r="461" spans="1:3">
+    <row r="461" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A461" t="s">
         <v>6</v>
       </c>
@@ -5446,7 +5467,7 @@
         <v>97.25</v>
       </c>
     </row>
-    <row r="462" spans="1:3">
+    <row r="462" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A462" t="s">
         <v>6</v>
       </c>
@@ -5457,7 +5478,7 @@
         <v>46.75</v>
       </c>
     </row>
-    <row r="463" spans="1:3">
+    <row r="463" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A463" t="s">
         <v>6</v>
       </c>
@@ -5468,7 +5489,7 @@
         <v>62.98</v>
       </c>
     </row>
-    <row r="464" spans="1:3">
+    <row r="464" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A464" t="s">
         <v>6</v>
       </c>
@@ -5479,7 +5500,7 @@
         <v>105.83</v>
       </c>
     </row>
-    <row r="465" spans="1:3">
+    <row r="465" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A465" t="s">
         <v>6</v>
       </c>
@@ -5487,10 +5508,10 @@
         <v>2764.32</v>
       </c>
       <c r="C465">
-        <v>95.51000000000001</v>
-      </c>
-    </row>
-    <row r="466" spans="1:3">
+        <v>95.51</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A466" t="s">
         <v>6</v>
       </c>
@@ -5498,10 +5519,10 @@
         <v>2657.63</v>
       </c>
       <c r="C466">
-        <v>73.45999999999999</v>
-      </c>
-    </row>
-    <row r="467" spans="1:3">
+        <v>73.459999999999994</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A467" t="s">
         <v>6</v>
       </c>
@@ -5509,10 +5530,10 @@
         <v>2703.76</v>
       </c>
       <c r="C467">
-        <v>67.79000000000001</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3">
+        <v>67.790000000000006</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A468" t="s">
         <v>6</v>
       </c>
@@ -5523,7 +5544,7 @@
         <v>104.43</v>
       </c>
     </row>
-    <row r="469" spans="1:3">
+    <row r="469" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
         <v>6</v>
       </c>
@@ -5534,7 +5555,7 @@
         <v>58.75</v>
       </c>
     </row>
-    <row r="470" spans="1:3">
+    <row r="470" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A470" t="s">
         <v>6</v>
       </c>
@@ -5545,7 +5566,7 @@
         <v>59.78</v>
       </c>
     </row>
-    <row r="471" spans="1:3">
+    <row r="471" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A471" t="s">
         <v>6</v>
       </c>
@@ -5556,7 +5577,7 @@
         <v>47.22</v>
       </c>
     </row>
-    <row r="472" spans="1:3">
+    <row r="472" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A472" t="s">
         <v>6</v>
       </c>
@@ -5567,7 +5588,7 @@
         <v>86.94</v>
       </c>
     </row>
-    <row r="473" spans="1:3">
+    <row r="473" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A473" t="s">
         <v>6</v>
       </c>
@@ -5578,7 +5599,7 @@
         <v>96.33</v>
       </c>
     </row>
-    <row r="474" spans="1:3">
+    <row r="474" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A474" t="s">
         <v>6</v>
       </c>
@@ -5589,7 +5610,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="475" spans="1:3">
+    <row r="475" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A475" t="s">
         <v>6</v>
       </c>
@@ -5597,10 +5618,10 @@
         <v>2709.47</v>
       </c>
       <c r="C475">
-        <v>92.98999999999999</v>
-      </c>
-    </row>
-    <row r="476" spans="1:3">
+        <v>92.99</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A476" t="s">
         <v>6</v>
       </c>
@@ -5611,7 +5632,7 @@
         <v>90.45</v>
       </c>
     </row>
-    <row r="477" spans="1:3">
+    <row r="477" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A477" t="s">
         <v>7</v>
       </c>
@@ -5622,18 +5643,18 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="478" spans="1:3">
+    <row r="478" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
         <v>7</v>
       </c>
       <c r="B478">
-        <v>96.51000000000001</v>
+        <v>96.51</v>
       </c>
       <c r="C478">
         <v>2.75</v>
       </c>
     </row>
-    <row r="479" spans="1:3">
+    <row r="479" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A479" t="s">
         <v>7</v>
       </c>
@@ -5644,7 +5665,7 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="480" spans="1:3">
+    <row r="480" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A480" t="s">
         <v>7</v>
       </c>
@@ -5655,7 +5676,7 @@
         <v>2.12</v>
       </c>
     </row>
-    <row r="481" spans="1:3">
+    <row r="481" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A481" t="s">
         <v>7</v>
       </c>
@@ -5666,7 +5687,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="482" spans="1:3">
+    <row r="482" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A482" t="s">
         <v>7</v>
       </c>
@@ -5674,10 +5695,10 @@
         <v>132.85</v>
       </c>
       <c r="C482">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="483" spans="1:3">
+        <v>2.5499999999999998</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A483" t="s">
         <v>7</v>
       </c>
@@ -5688,7 +5709,7 @@
         <v>22.09</v>
       </c>
     </row>
-    <row r="484" spans="1:3">
+    <row r="484" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A484" t="s">
         <v>7</v>
       </c>
@@ -5699,29 +5720,29 @@
         <v>32.67</v>
       </c>
     </row>
-    <row r="485" spans="1:3">
+    <row r="485" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A485" t="s">
         <v>7</v>
       </c>
       <c r="B485">
-        <v>992.5700000000001</v>
+        <v>992.57</v>
       </c>
       <c r="C485">
         <v>27.81</v>
       </c>
     </row>
-    <row r="486" spans="1:3">
+    <row r="486" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A486" t="s">
         <v>7</v>
       </c>
       <c r="B486">
-        <v>1103.12</v>
+        <v>1103.1199999999999</v>
       </c>
       <c r="C486">
         <v>38.44</v>
       </c>
     </row>
-    <row r="487" spans="1:3">
+    <row r="487" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
         <v>7</v>
       </c>
@@ -5732,7 +5753,7 @@
         <v>33.61</v>
       </c>
     </row>
-    <row r="488" spans="1:3">
+    <row r="488" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A488" t="s">
         <v>7</v>
       </c>
@@ -5743,7 +5764,7 @@
         <v>18.34</v>
       </c>
     </row>
-    <row r="489" spans="1:3">
+    <row r="489" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
         <v>7</v>
       </c>
@@ -5754,29 +5775,29 @@
         <v>28.29</v>
       </c>
     </row>
-    <row r="490" spans="1:3">
+    <row r="490" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
         <v>7</v>
       </c>
       <c r="B490">
-        <v>1064.09</v>
+        <v>1064.0899999999999</v>
       </c>
       <c r="C490">
         <v>42.03</v>
       </c>
     </row>
-    <row r="491" spans="1:3">
+    <row r="491" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A491" t="s">
         <v>7</v>
       </c>
       <c r="B491">
-        <v>1062.13</v>
+        <v>1062.1300000000001</v>
       </c>
       <c r="C491">
         <v>24.81</v>
       </c>
     </row>
-    <row r="492" spans="1:3">
+    <row r="492" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A492" t="s">
         <v>7</v>
       </c>
@@ -5787,18 +5808,18 @@
         <v>22.75</v>
       </c>
     </row>
-    <row r="493" spans="1:3">
+    <row r="493" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A493" t="s">
         <v>7</v>
       </c>
       <c r="B493">
-        <v>1091.13</v>
+        <v>1091.1300000000001</v>
       </c>
       <c r="C493">
         <v>40.69</v>
       </c>
     </row>
-    <row r="494" spans="1:3">
+    <row r="494" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A494" t="s">
         <v>7</v>
       </c>
@@ -5809,18 +5830,18 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="495" spans="1:3">
+    <row r="495" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A495" t="s">
         <v>7</v>
       </c>
       <c r="B495">
-        <v>1145.59</v>
+        <v>1145.5899999999999</v>
       </c>
       <c r="C495">
         <v>29.54</v>
       </c>
     </row>
-    <row r="496" spans="1:3">
+    <row r="496" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
         <v>7</v>
       </c>
@@ -5831,7 +5852,7 @@
         <v>44.16</v>
       </c>
     </row>
-    <row r="497" spans="1:3">
+    <row r="497" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
         <v>7</v>
       </c>
@@ -5842,7 +5863,7 @@
         <v>41.4</v>
       </c>
     </row>
-    <row r="498" spans="1:3">
+    <row r="498" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A498" t="s">
         <v>7</v>
       </c>
@@ -5853,7 +5874,7 @@
         <v>21.92</v>
       </c>
     </row>
-    <row r="499" spans="1:3">
+    <row r="499" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A499" t="s">
         <v>7</v>
       </c>
@@ -5864,7 +5885,7 @@
         <v>20.05</v>
       </c>
     </row>
-    <row r="500" spans="1:3">
+    <row r="500" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A500" t="s">
         <v>7</v>
       </c>
@@ -5875,7 +5896,7 @@
         <v>27.66</v>
       </c>
     </row>
-    <row r="501" spans="1:3">
+    <row r="501" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A501" t="s">
         <v>7</v>
       </c>
@@ -5886,7 +5907,7 @@
         <v>36.24</v>
       </c>
     </row>
-    <row r="502" spans="1:3">
+    <row r="502" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A502" t="s">
         <v>7</v>
       </c>
@@ -5894,10 +5915,10 @@
         <v>1073.97</v>
       </c>
       <c r="C502">
-        <v>38.09</v>
-      </c>
-    </row>
-    <row r="503" spans="1:3">
+        <v>38.090000000000003</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A503" t="s">
         <v>7</v>
       </c>
@@ -5908,18 +5929,18 @@
         <v>24.08</v>
       </c>
     </row>
-    <row r="504" spans="1:3">
+    <row r="504" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A504" t="s">
         <v>7</v>
       </c>
       <c r="B504">
-        <v>1075.14</v>
+        <v>1075.1400000000001</v>
       </c>
       <c r="C504">
         <v>28.2</v>
       </c>
     </row>
-    <row r="505" spans="1:3">
+    <row r="505" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
         <v>7</v>
       </c>
@@ -5930,18 +5951,18 @@
         <v>29.51</v>
       </c>
     </row>
-    <row r="506" spans="1:3">
+    <row r="506" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A506" t="s">
         <v>7</v>
       </c>
       <c r="B506">
-        <v>1088.13</v>
+        <v>1088.1300000000001</v>
       </c>
       <c r="C506">
         <v>25.36</v>
       </c>
     </row>
-    <row r="507" spans="1:3">
+    <row r="507" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A507" t="s">
         <v>7</v>
       </c>
@@ -5952,7 +5973,7 @@
         <v>37.58</v>
       </c>
     </row>
-    <row r="508" spans="1:3">
+    <row r="508" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A508" t="s">
         <v>7</v>
       </c>
@@ -5963,7 +5984,7 @@
         <v>31.24</v>
       </c>
     </row>
-    <row r="509" spans="1:3">
+    <row r="509" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A509" t="s">
         <v>7</v>
       </c>
@@ -5974,7 +5995,7 @@
         <v>27.41</v>
       </c>
     </row>
-    <row r="510" spans="1:3">
+    <row r="510" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A510" t="s">
         <v>7</v>
       </c>
@@ -5985,7 +6006,7 @@
         <v>37.51</v>
       </c>
     </row>
-    <row r="511" spans="1:3">
+    <row r="511" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A511" t="s">
         <v>7</v>
       </c>
@@ -5996,29 +6017,29 @@
         <v>24.22</v>
       </c>
     </row>
-    <row r="512" spans="1:3">
+    <row r="512" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A512" t="s">
         <v>7</v>
       </c>
       <c r="B512">
-        <v>1078.91</v>
+        <v>1078.9100000000001</v>
       </c>
       <c r="C512">
         <v>32.86</v>
       </c>
     </row>
-    <row r="513" spans="1:3">
+    <row r="513" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A513" t="s">
         <v>7</v>
       </c>
       <c r="B513">
-        <v>1069.59</v>
+        <v>1069.5899999999999</v>
       </c>
       <c r="C513">
         <v>37.18</v>
       </c>
     </row>
-    <row r="514" spans="1:3">
+    <row r="514" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
         <v>7</v>
       </c>
@@ -6029,7 +6050,7 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="515" spans="1:3">
+    <row r="515" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A515" t="s">
         <v>7</v>
       </c>
@@ -6040,7 +6061,7 @@
         <v>19.71</v>
       </c>
     </row>
-    <row r="516" spans="1:3">
+    <row r="516" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A516" t="s">
         <v>7</v>
       </c>
@@ -6051,7 +6072,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="517" spans="1:3">
+    <row r="517" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A517" t="s">
         <v>7</v>
       </c>
@@ -6062,7 +6083,7 @@
         <v>37.46</v>
       </c>
     </row>
-    <row r="518" spans="1:3">
+    <row r="518" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A518" t="s">
         <v>7</v>
       </c>
@@ -6070,10 +6091,10 @@
         <v>1059.03</v>
       </c>
       <c r="C518">
-        <v>37.62</v>
-      </c>
-    </row>
-    <row r="519" spans="1:3">
+        <v>37.619999999999997</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A519" t="s">
         <v>7</v>
       </c>
@@ -6081,10 +6102,10 @@
         <v>1106.99</v>
       </c>
       <c r="C519">
-        <v>36.66</v>
-      </c>
-    </row>
-    <row r="520" spans="1:3">
+        <v>36.659999999999997</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A520" t="s">
         <v>7</v>
       </c>
@@ -6095,18 +6116,18 @@
         <v>16.66</v>
       </c>
     </row>
-    <row r="521" spans="1:3">
+    <row r="521" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A521" t="s">
         <v>7</v>
       </c>
       <c r="B521">
-        <v>1031.9</v>
+        <v>1031.9000000000001</v>
       </c>
       <c r="C521">
         <v>22.86</v>
       </c>
     </row>
-    <row r="522" spans="1:3">
+    <row r="522" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A522" t="s">
         <v>7</v>
       </c>
@@ -6117,7 +6138,7 @@
         <v>41.41</v>
       </c>
     </row>
-    <row r="523" spans="1:3">
+    <row r="523" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
         <v>7</v>
       </c>
@@ -6128,7 +6149,7 @@
         <v>32.35</v>
       </c>
     </row>
-    <row r="524" spans="1:3">
+    <row r="524" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A524" t="s">
         <v>7</v>
       </c>
@@ -6139,7 +6160,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="525" spans="1:3">
+    <row r="525" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A525" t="s">
         <v>7</v>
       </c>
@@ -6150,7 +6171,7 @@
         <v>40.98</v>
       </c>
     </row>
-    <row r="526" spans="1:3">
+    <row r="526" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A526" t="s">
         <v>7</v>
       </c>
@@ -6158,21 +6179,21 @@
         <v>1022.32</v>
       </c>
       <c r="C526">
-        <v>40.13</v>
-      </c>
-    </row>
-    <row r="527" spans="1:3">
+        <v>40.130000000000003</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A527" t="s">
         <v>7</v>
       </c>
       <c r="B527">
-        <v>1098.15</v>
+        <v>1098.1500000000001</v>
       </c>
       <c r="C527">
         <v>24.17</v>
       </c>
     </row>
-    <row r="528" spans="1:3">
+    <row r="528" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A528" t="s">
         <v>7</v>
       </c>
@@ -6183,7 +6204,7 @@
         <v>38.29</v>
       </c>
     </row>
-    <row r="529" spans="1:3">
+    <row r="529" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A529" t="s">
         <v>7</v>
       </c>
@@ -6191,32 +6212,32 @@
         <v>1087.76</v>
       </c>
       <c r="C529">
-        <v>38.73</v>
-      </c>
-    </row>
-    <row r="530" spans="1:3">
+        <v>38.729999999999997</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A530" t="s">
         <v>7</v>
       </c>
       <c r="B530">
-        <v>1080.35</v>
+        <v>1080.3499999999999</v>
       </c>
       <c r="C530">
-        <v>39.38</v>
-      </c>
-    </row>
-    <row r="531" spans="1:3">
+        <v>39.380000000000003</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A531" t="s">
         <v>7</v>
       </c>
       <c r="B531">
-        <v>1094.41</v>
+        <v>1094.4100000000001</v>
       </c>
       <c r="C531">
         <v>41.51</v>
       </c>
     </row>
-    <row r="532" spans="1:3">
+    <row r="532" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
         <v>7</v>
       </c>
@@ -6224,10 +6245,10 @@
         <v>1018.15</v>
       </c>
       <c r="C532">
-        <v>34.66</v>
-      </c>
-    </row>
-    <row r="533" spans="1:3">
+        <v>34.659999999999997</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A533" t="s">
         <v>7</v>
       </c>
@@ -6238,7 +6259,7 @@
         <v>30.17</v>
       </c>
     </row>
-    <row r="534" spans="1:3">
+    <row r="534" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A534" t="s">
         <v>7</v>
       </c>
@@ -6249,7 +6270,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="535" spans="1:3">
+    <row r="535" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A535" t="s">
         <v>7</v>
       </c>
@@ -6260,7 +6281,7 @@
         <v>36.36</v>
       </c>
     </row>
-    <row r="536" spans="1:3">
+    <row r="536" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A536" t="s">
         <v>7</v>
       </c>
@@ -6271,7 +6292,7 @@
         <v>54.06</v>
       </c>
     </row>
-    <row r="537" spans="1:3">
+    <row r="537" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A537" t="s">
         <v>7</v>
       </c>
@@ -6282,7 +6303,7 @@
         <v>48.23</v>
       </c>
     </row>
-    <row r="538" spans="1:3">
+    <row r="538" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A538" t="s">
         <v>7</v>
       </c>
@@ -6293,7 +6314,7 @@
         <v>70.69</v>
       </c>
     </row>
-    <row r="539" spans="1:3">
+    <row r="539" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A539" t="s">
         <v>7</v>
       </c>
@@ -6304,7 +6325,7 @@
         <v>39.79</v>
       </c>
     </row>
-    <row r="540" spans="1:3">
+    <row r="540" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A540" t="s">
         <v>7</v>
       </c>
@@ -6315,7 +6336,7 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="541" spans="1:3">
+    <row r="541" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
         <v>7</v>
       </c>
@@ -6326,7 +6347,7 @@
         <v>29.33</v>
       </c>
     </row>
-    <row r="542" spans="1:3">
+    <row r="542" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A542" t="s">
         <v>7</v>
       </c>
@@ -6334,10 +6355,10 @@
         <v>1746.03</v>
       </c>
       <c r="C542">
-        <v>36.3</v>
-      </c>
-    </row>
-    <row r="543" spans="1:3">
+        <v>36.299999999999997</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A543" t="s">
         <v>7</v>
       </c>
@@ -6345,10 +6366,10 @@
         <v>1777.08</v>
       </c>
       <c r="C543">
-        <v>66.56999999999999</v>
-      </c>
-    </row>
-    <row r="544" spans="1:3">
+        <v>66.569999999999993</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A544" t="s">
         <v>7</v>
       </c>
@@ -6359,7 +6380,7 @@
         <v>50.48</v>
       </c>
     </row>
-    <row r="545" spans="1:3">
+    <row r="545" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A545" t="s">
         <v>7</v>
       </c>
@@ -6367,10 +6388,10 @@
         <v>1826.78</v>
       </c>
       <c r="C545">
-        <v>40.09</v>
-      </c>
-    </row>
-    <row r="546" spans="1:3">
+        <v>40.090000000000003</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A546" t="s">
         <v>7</v>
       </c>
@@ -6381,7 +6402,7 @@
         <v>50.77</v>
       </c>
     </row>
-    <row r="547" spans="1:3">
+    <row r="547" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A547" t="s">
         <v>7</v>
       </c>
@@ -6392,7 +6413,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="548" spans="1:3">
+    <row r="548" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A548" t="s">
         <v>7</v>
       </c>
@@ -6403,7 +6424,7 @@
         <v>41.59</v>
       </c>
     </row>
-    <row r="549" spans="1:3">
+    <row r="549" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A549" t="s">
         <v>7</v>
       </c>
@@ -6414,7 +6435,7 @@
         <v>28.09</v>
       </c>
     </row>
-    <row r="550" spans="1:3">
+    <row r="550" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A550" t="s">
         <v>7</v>
       </c>
@@ -6425,7 +6446,7 @@
         <v>56.56</v>
       </c>
     </row>
-    <row r="551" spans="1:3">
+    <row r="551" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A551" t="s">
         <v>7</v>
       </c>
@@ -6436,7 +6457,7 @@
         <v>53.42</v>
       </c>
     </row>
-    <row r="552" spans="1:3">
+    <row r="552" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A552" t="s">
         <v>7</v>
       </c>
@@ -6447,7 +6468,7 @@
         <v>30.12</v>
       </c>
     </row>
-    <row r="553" spans="1:3">
+    <row r="553" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A553" t="s">
         <v>7</v>
       </c>
@@ -6458,7 +6479,7 @@
         <v>47.89</v>
       </c>
     </row>
-    <row r="554" spans="1:3">
+    <row r="554" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A554" t="s">
         <v>7</v>
       </c>
@@ -6466,10 +6487,10 @@
         <v>1701.07</v>
       </c>
       <c r="C554">
-        <v>33.12</v>
-      </c>
-    </row>
-    <row r="555" spans="1:3">
+        <v>33.119999999999997</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A555" t="s">
         <v>7</v>
       </c>
@@ -6480,7 +6501,7 @@
         <v>42.18</v>
       </c>
     </row>
-    <row r="556" spans="1:3">
+    <row r="556" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A556" t="s">
         <v>7</v>
       </c>
@@ -6491,7 +6512,7 @@
         <v>60.77</v>
       </c>
     </row>
-    <row r="557" spans="1:3">
+    <row r="557" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A557" t="s">
         <v>7</v>
       </c>
@@ -6502,7 +6523,7 @@
         <v>53.81</v>
       </c>
     </row>
-    <row r="558" spans="1:3">
+    <row r="558" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A558" t="s">
         <v>7</v>
       </c>
@@ -6513,7 +6534,7 @@
         <v>41.38</v>
       </c>
     </row>
-    <row r="559" spans="1:3">
+    <row r="559" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A559" t="s">
         <v>7</v>
       </c>
@@ -6524,7 +6545,7 @@
         <v>61.87</v>
       </c>
     </row>
-    <row r="560" spans="1:3">
+    <row r="560" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A560" t="s">
         <v>7</v>
       </c>
@@ -6535,7 +6556,7 @@
         <v>36.92</v>
       </c>
     </row>
-    <row r="561" spans="1:3">
+    <row r="561" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A561" t="s">
         <v>7</v>
       </c>
@@ -6546,7 +6567,7 @@
         <v>54.59</v>
       </c>
     </row>
-    <row r="562" spans="1:3">
+    <row r="562" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A562" t="s">
         <v>7</v>
       </c>
@@ -6557,7 +6578,7 @@
         <v>42.22</v>
       </c>
     </row>
-    <row r="563" spans="1:3">
+    <row r="563" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A563" t="s">
         <v>7</v>
       </c>
@@ -6568,7 +6589,7 @@
         <v>55.74</v>
       </c>
     </row>
-    <row r="564" spans="1:3">
+    <row r="564" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A564" t="s">
         <v>7</v>
       </c>
@@ -6579,7 +6600,7 @@
         <v>47.57</v>
       </c>
     </row>
-    <row r="565" spans="1:3">
+    <row r="565" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A565" t="s">
         <v>7</v>
       </c>
@@ -6590,7 +6611,7 @@
         <v>46.59</v>
       </c>
     </row>
-    <row r="566" spans="1:3">
+    <row r="566" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A566" t="s">
         <v>7</v>
       </c>
@@ -6601,7 +6622,7 @@
         <v>60.54</v>
       </c>
     </row>
-    <row r="567" spans="1:3">
+    <row r="567" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A567" t="s">
         <v>7</v>
       </c>
@@ -6612,7 +6633,7 @@
         <v>63.7</v>
       </c>
     </row>
-    <row r="568" spans="1:3">
+    <row r="568" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A568" t="s">
         <v>7</v>
       </c>
@@ -6623,7 +6644,7 @@
         <v>67.25</v>
       </c>
     </row>
-    <row r="569" spans="1:3">
+    <row r="569" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A569" t="s">
         <v>7</v>
       </c>
@@ -6634,7 +6655,7 @@
         <v>36.79</v>
       </c>
     </row>
-    <row r="570" spans="1:3">
+    <row r="570" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A570" t="s">
         <v>7</v>
       </c>
@@ -6642,10 +6663,10 @@
         <v>1766.5</v>
       </c>
       <c r="C570">
-        <v>69.98999999999999</v>
-      </c>
-    </row>
-    <row r="571" spans="1:3">
+        <v>69.989999999999995</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A571" t="s">
         <v>7</v>
       </c>
@@ -6656,7 +6677,7 @@
         <v>53.74</v>
       </c>
     </row>
-    <row r="572" spans="1:3">
+    <row r="572" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A572" t="s">
         <v>7</v>
       </c>
@@ -6664,10 +6685,10 @@
         <v>1742.77</v>
       </c>
       <c r="C572">
-        <v>34.09</v>
-      </c>
-    </row>
-    <row r="573" spans="1:3">
+        <v>34.090000000000003</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A573" t="s">
         <v>7</v>
       </c>
@@ -6678,7 +6699,7 @@
         <v>44.28</v>
       </c>
     </row>
-    <row r="574" spans="1:3">
+    <row r="574" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A574" t="s">
         <v>7</v>
       </c>
@@ -6689,7 +6710,7 @@
         <v>59.33</v>
       </c>
     </row>
-    <row r="575" spans="1:3">
+    <row r="575" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A575" t="s">
         <v>7</v>
       </c>
@@ -6697,10 +6718,10 @@
         <v>2723.66</v>
       </c>
       <c r="C575">
-        <v>73.18000000000001</v>
-      </c>
-    </row>
-    <row r="576" spans="1:3">
+        <v>73.180000000000007</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A576" t="s">
         <v>7</v>
       </c>
@@ -6711,7 +6732,7 @@
         <v>82.62</v>
       </c>
     </row>
-    <row r="577" spans="1:3">
+    <row r="577" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
         <v>7</v>
       </c>
@@ -6722,7 +6743,7 @@
         <v>101.99</v>
       </c>
     </row>
-    <row r="578" spans="1:3">
+    <row r="578" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A578" t="s">
         <v>7</v>
       </c>
@@ -6733,7 +6754,7 @@
         <v>95.87</v>
       </c>
     </row>
-    <row r="579" spans="1:3">
+    <row r="579" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A579" t="s">
         <v>7</v>
       </c>
@@ -6744,7 +6765,7 @@
         <v>106.68</v>
       </c>
     </row>
-    <row r="580" spans="1:3">
+    <row r="580" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A580" t="s">
         <v>7</v>
       </c>
@@ -6755,7 +6776,7 @@
         <v>107.44</v>
       </c>
     </row>
-    <row r="581" spans="1:3">
+    <row r="581" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A581" t="s">
         <v>7</v>
       </c>
@@ -6763,10 +6784,10 @@
         <v>2627.11</v>
       </c>
       <c r="C581">
-        <v>96.93000000000001</v>
-      </c>
-    </row>
-    <row r="582" spans="1:3">
+        <v>96.93</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A582" t="s">
         <v>7</v>
       </c>
@@ -6774,10 +6795,10 @@
         <v>2505.17</v>
       </c>
       <c r="C582">
-        <v>99.20999999999999</v>
-      </c>
-    </row>
-    <row r="583" spans="1:3">
+        <v>99.21</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A583" t="s">
         <v>7</v>
       </c>
@@ -6788,7 +6809,7 @@
         <v>90.2</v>
       </c>
     </row>
-    <row r="584" spans="1:3">
+    <row r="584" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A584" t="s">
         <v>7</v>
       </c>
@@ -6799,7 +6820,7 @@
         <v>53.57</v>
       </c>
     </row>
-    <row r="585" spans="1:3">
+    <row r="585" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A585" t="s">
         <v>7</v>
       </c>
@@ -6807,10 +6828,10 @@
         <v>2779.26</v>
       </c>
       <c r="C585">
-        <v>82.81999999999999</v>
-      </c>
-    </row>
-    <row r="586" spans="1:3">
+        <v>82.82</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A586" t="s">
         <v>7</v>
       </c>
@@ -6821,7 +6842,7 @@
         <v>74.45</v>
       </c>
     </row>
-    <row r="587" spans="1:3">
+    <row r="587" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A587" t="s">
         <v>7</v>
       </c>
@@ -6832,7 +6853,7 @@
         <v>84.87</v>
       </c>
     </row>
-    <row r="588" spans="1:3">
+    <row r="588" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A588" t="s">
         <v>7</v>
       </c>
@@ -6843,7 +6864,7 @@
         <v>60.11</v>
       </c>
     </row>
-    <row r="589" spans="1:3">
+    <row r="589" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A589" t="s">
         <v>7</v>
       </c>
@@ -6854,7 +6875,7 @@
         <v>106.82</v>
       </c>
     </row>
-    <row r="590" spans="1:3">
+    <row r="590" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A590" t="s">
         <v>7</v>
       </c>
@@ -6865,7 +6886,7 @@
         <v>59.23</v>
       </c>
     </row>
-    <row r="591" spans="1:3">
+    <row r="591" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A591" t="s">
         <v>7</v>
       </c>
@@ -6876,7 +6897,7 @@
         <v>75.12</v>
       </c>
     </row>
-    <row r="592" spans="1:3">
+    <row r="592" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A592" t="s">
         <v>7</v>
       </c>
@@ -6887,7 +6908,7 @@
         <v>53.72</v>
       </c>
     </row>
-    <row r="593" spans="1:3">
+    <row r="593" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A593" t="s">
         <v>7</v>
       </c>
@@ -6898,7 +6919,7 @@
         <v>104.84</v>
       </c>
     </row>
-    <row r="594" spans="1:3">
+    <row r="594" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A594" t="s">
         <v>7</v>
       </c>
@@ -6909,7 +6930,7 @@
         <v>103.25</v>
       </c>
     </row>
-    <row r="595" spans="1:3">
+    <row r="595" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A595" t="s">
         <v>8</v>
       </c>
@@ -6920,7 +6941,7 @@
         <v>43.99</v>
       </c>
     </row>
-    <row r="596" spans="1:3">
+    <row r="596" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A596" t="s">
         <v>8</v>
       </c>
@@ -6931,7 +6952,7 @@
         <v>24.13</v>
       </c>
     </row>
-    <row r="597" spans="1:3">
+    <row r="597" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A597" t="s">
         <v>8</v>
       </c>
@@ -6942,18 +6963,18 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="598" spans="1:3">
+    <row r="598" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A598" t="s">
         <v>8</v>
       </c>
       <c r="B598">
-        <v>1109.88</v>
+        <v>1109.8800000000001</v>
       </c>
       <c r="C598">
         <v>42.08</v>
       </c>
     </row>
-    <row r="599" spans="1:3">
+    <row r="599" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A599" t="s">
         <v>8</v>
       </c>
@@ -6964,7 +6985,7 @@
         <v>40.68</v>
       </c>
     </row>
-    <row r="600" spans="1:3">
+    <row r="600" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A600" t="s">
         <v>8</v>
       </c>
@@ -6975,18 +6996,18 @@
         <v>20.81</v>
       </c>
     </row>
-    <row r="601" spans="1:3">
+    <row r="601" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A601" t="s">
         <v>8</v>
       </c>
       <c r="B601">
-        <v>1156.66</v>
+        <v>1156.6600000000001</v>
       </c>
       <c r="C601">
         <v>31.44</v>
       </c>
     </row>
-    <row r="602" spans="1:3">
+    <row r="602" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A602" t="s">
         <v>8</v>
       </c>
@@ -6994,32 +7015,32 @@
         <v>1081.44</v>
       </c>
       <c r="C602">
-        <v>18.76</v>
-      </c>
-    </row>
-    <row r="603" spans="1:3">
+        <v>18.760000000000002</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A603" t="s">
         <v>8</v>
       </c>
       <c r="B603">
-        <v>1059.4</v>
+        <v>1059.4000000000001</v>
       </c>
       <c r="C603">
         <v>38.03</v>
       </c>
     </row>
-    <row r="604" spans="1:3">
+    <row r="604" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A604" t="s">
         <v>8</v>
       </c>
       <c r="B604">
-        <v>1058.59</v>
+        <v>1058.5899999999999</v>
       </c>
       <c r="C604">
         <v>38.28</v>
       </c>
     </row>
-    <row r="605" spans="1:3">
+    <row r="605" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A605" t="s">
         <v>8</v>
       </c>
@@ -7030,18 +7051,18 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="606" spans="1:3">
+    <row r="606" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A606" t="s">
         <v>8</v>
       </c>
       <c r="B606">
-        <v>1132.63</v>
+        <v>1132.6300000000001</v>
       </c>
       <c r="C606">
         <v>40.22</v>
       </c>
     </row>
-    <row r="607" spans="1:3">
+    <row r="607" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A607" t="s">
         <v>8</v>
       </c>
@@ -7052,7 +7073,7 @@
         <v>27.56</v>
       </c>
     </row>
-    <row r="608" spans="1:3">
+    <row r="608" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A608" t="s">
         <v>8</v>
       </c>
@@ -7063,7 +7084,7 @@
         <v>28.88</v>
       </c>
     </row>
-    <row r="609" spans="1:3">
+    <row r="609" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A609" t="s">
         <v>8</v>
       </c>
@@ -7074,7 +7095,7 @@
         <v>35.29</v>
       </c>
     </row>
-    <row r="610" spans="1:3">
+    <row r="610" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A610" t="s">
         <v>8</v>
       </c>
@@ -7085,7 +7106,7 @@
         <v>28.36</v>
       </c>
     </row>
-    <row r="611" spans="1:3">
+    <row r="611" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A611" t="s">
         <v>8</v>
       </c>
@@ -7093,10 +7114,10 @@
         <v>1028.42</v>
       </c>
       <c r="C611">
-        <v>40.16</v>
-      </c>
-    </row>
-    <row r="612" spans="1:3">
+        <v>40.159999999999997</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A612" t="s">
         <v>8</v>
       </c>
@@ -7107,7 +7128,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="613" spans="1:3">
+    <row r="613" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A613" t="s">
         <v>8</v>
       </c>
@@ -7118,7 +7139,7 @@
         <v>30.5</v>
       </c>
     </row>
-    <row r="614" spans="1:3">
+    <row r="614" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A614" t="s">
         <v>8</v>
       </c>
@@ -7129,29 +7150,29 @@
         <v>39.67</v>
       </c>
     </row>
-    <row r="615" spans="1:3">
+    <row r="615" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A615" t="s">
         <v>8</v>
       </c>
       <c r="B615">
-        <v>1154.6</v>
+        <v>1154.5999999999999</v>
       </c>
       <c r="C615">
         <v>25.7</v>
       </c>
     </row>
-    <row r="616" spans="1:3">
+    <row r="616" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A616" t="s">
         <v>8</v>
       </c>
       <c r="B616">
-        <v>1177.39</v>
+        <v>1177.3900000000001</v>
       </c>
       <c r="C616">
         <v>28.1</v>
       </c>
     </row>
-    <row r="617" spans="1:3">
+    <row r="617" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A617" t="s">
         <v>8</v>
       </c>
@@ -7162,18 +7183,18 @@
         <v>19.84</v>
       </c>
     </row>
-    <row r="618" spans="1:3">
+    <row r="618" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A618" t="s">
         <v>8</v>
       </c>
       <c r="B618">
-        <v>1119.59</v>
+        <v>1119.5899999999999</v>
       </c>
       <c r="C618">
         <v>42.81</v>
       </c>
     </row>
-    <row r="619" spans="1:3">
+    <row r="619" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A619" t="s">
         <v>8</v>
       </c>
@@ -7184,29 +7205,29 @@
         <v>34.68</v>
       </c>
     </row>
-    <row r="620" spans="1:3">
+    <row r="620" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A620" t="s">
         <v>8</v>
       </c>
       <c r="B620">
-        <v>1156.59</v>
+        <v>1156.5899999999999</v>
       </c>
       <c r="C620">
         <v>30.85</v>
       </c>
     </row>
-    <row r="621" spans="1:3">
+    <row r="621" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A621" t="s">
         <v>8</v>
       </c>
       <c r="B621">
-        <v>1050.11</v>
+        <v>1050.1099999999999</v>
       </c>
       <c r="C621">
         <v>39.28</v>
       </c>
     </row>
-    <row r="622" spans="1:3">
+    <row r="622" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A622" t="s">
         <v>8</v>
       </c>
@@ -7217,18 +7238,18 @@
         <v>41.45</v>
       </c>
     </row>
-    <row r="623" spans="1:3">
+    <row r="623" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A623" t="s">
         <v>8</v>
       </c>
       <c r="B623">
-        <v>1087.15</v>
+        <v>1087.1500000000001</v>
       </c>
       <c r="C623">
         <v>22.83</v>
       </c>
     </row>
-    <row r="624" spans="1:3">
+    <row r="624" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A624" t="s">
         <v>8</v>
       </c>
@@ -7239,7 +7260,7 @@
         <v>20.66</v>
       </c>
     </row>
-    <row r="625" spans="1:3">
+    <row r="625" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A625" t="s">
         <v>8</v>
       </c>
@@ -7247,32 +7268,32 @@
         <v>976.79</v>
       </c>
       <c r="C625">
-        <v>36.27</v>
-      </c>
-    </row>
-    <row r="626" spans="1:3">
+        <v>36.270000000000003</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A626" t="s">
         <v>8</v>
       </c>
       <c r="B626">
-        <v>1132.85</v>
+        <v>1132.8499999999999</v>
       </c>
       <c r="C626">
         <v>44.14</v>
       </c>
     </row>
-    <row r="627" spans="1:3">
+    <row r="627" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A627" t="s">
         <v>8</v>
       </c>
       <c r="B627">
-        <v>1063.16</v>
+        <v>1063.1600000000001</v>
       </c>
       <c r="C627">
         <v>30.87</v>
       </c>
     </row>
-    <row r="628" spans="1:3">
+    <row r="628" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A628" t="s">
         <v>8</v>
       </c>
@@ -7283,7 +7304,7 @@
         <v>36.94</v>
       </c>
     </row>
-    <row r="629" spans="1:3">
+    <row r="629" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A629" t="s">
         <v>8</v>
       </c>
@@ -7291,10 +7312,10 @@
         <v>1088.19</v>
       </c>
       <c r="C629">
-        <v>17.92</v>
-      </c>
-    </row>
-    <row r="630" spans="1:3">
+        <v>17.920000000000002</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A630" t="s">
         <v>8</v>
       </c>
@@ -7305,7 +7326,7 @@
         <v>31.62</v>
       </c>
     </row>
-    <row r="631" spans="1:3">
+    <row r="631" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A631" t="s">
         <v>8</v>
       </c>
@@ -7316,7 +7337,7 @@
         <v>19.36</v>
       </c>
     </row>
-    <row r="632" spans="1:3">
+    <row r="632" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A632" t="s">
         <v>8</v>
       </c>
@@ -7327,18 +7348,18 @@
         <v>20.21</v>
       </c>
     </row>
-    <row r="633" spans="1:3">
+    <row r="633" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A633" t="s">
         <v>8</v>
       </c>
       <c r="B633">
-        <v>1121.62</v>
+        <v>1121.6199999999999</v>
       </c>
       <c r="C633">
-        <v>19.44</v>
-      </c>
-    </row>
-    <row r="634" spans="1:3">
+        <v>19.440000000000001</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A634" t="s">
         <v>8</v>
       </c>
@@ -7349,7 +7370,7 @@
         <v>33.64</v>
       </c>
     </row>
-    <row r="635" spans="1:3">
+    <row r="635" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A635" t="s">
         <v>8</v>
       </c>
@@ -7357,10 +7378,10 @@
         <v>1079.01</v>
       </c>
       <c r="C635">
-        <v>32.16</v>
-      </c>
-    </row>
-    <row r="636" spans="1:3">
+        <v>32.159999999999997</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A636" t="s">
         <v>8</v>
       </c>
@@ -7371,29 +7392,29 @@
         <v>30.61</v>
       </c>
     </row>
-    <row r="637" spans="1:3">
+    <row r="637" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A637" t="s">
         <v>8</v>
       </c>
       <c r="B637">
-        <v>1108.11</v>
+        <v>1108.1099999999999</v>
       </c>
       <c r="C637">
-        <v>36.77</v>
-      </c>
-    </row>
-    <row r="638" spans="1:3">
+        <v>36.770000000000003</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A638" t="s">
         <v>8</v>
       </c>
       <c r="B638">
-        <v>1068.36</v>
+        <v>1068.3599999999999</v>
       </c>
       <c r="C638">
         <v>19.22</v>
       </c>
     </row>
-    <row r="639" spans="1:3">
+    <row r="639" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A639" t="s">
         <v>8</v>
       </c>
@@ -7404,7 +7425,7 @@
         <v>25.27</v>
       </c>
     </row>
-    <row r="640" spans="1:3">
+    <row r="640" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A640" t="s">
         <v>8</v>
       </c>
@@ -7415,7 +7436,7 @@
         <v>21.34</v>
       </c>
     </row>
-    <row r="641" spans="1:3">
+    <row r="641" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A641" t="s">
         <v>8</v>
       </c>
@@ -7426,18 +7447,18 @@
         <v>32.29</v>
       </c>
     </row>
-    <row r="642" spans="1:3">
+    <row r="642" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A642" t="s">
         <v>8</v>
       </c>
       <c r="B642">
-        <v>1070.09</v>
+        <v>1070.0899999999999</v>
       </c>
       <c r="C642">
         <v>37.42</v>
       </c>
     </row>
-    <row r="643" spans="1:3">
+    <row r="643" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A643" t="s">
         <v>8</v>
       </c>
@@ -7448,7 +7469,7 @@
         <v>22.64</v>
       </c>
     </row>
-    <row r="644" spans="1:3">
+    <row r="644" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A644" t="s">
         <v>8</v>
       </c>
@@ -7456,21 +7477,21 @@
         <v>1033.29</v>
       </c>
       <c r="C644">
-        <v>38.87</v>
-      </c>
-    </row>
-    <row r="645" spans="1:3">
+        <v>38.869999999999997</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A645" t="s">
         <v>8</v>
       </c>
       <c r="B645">
-        <v>1053.12</v>
+        <v>1053.1199999999999</v>
       </c>
       <c r="C645">
         <v>25.71</v>
       </c>
     </row>
-    <row r="646" spans="1:3">
+    <row r="646" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A646" t="s">
         <v>8</v>
       </c>
@@ -7481,7 +7502,7 @@
         <v>23.84</v>
       </c>
     </row>
-    <row r="647" spans="1:3">
+    <row r="647" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A647" t="s">
         <v>8</v>
       </c>
@@ -7492,7 +7513,7 @@
         <v>37.94</v>
       </c>
     </row>
-    <row r="648" spans="1:3">
+    <row r="648" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A648" t="s">
         <v>8</v>
       </c>
@@ -7503,7 +7524,7 @@
         <v>58.77</v>
       </c>
     </row>
-    <row r="649" spans="1:3">
+    <row r="649" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A649" t="s">
         <v>8</v>
       </c>
@@ -7514,7 +7535,7 @@
         <v>27.13</v>
       </c>
     </row>
-    <row r="650" spans="1:3">
+    <row r="650" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A650" t="s">
         <v>8</v>
       </c>
@@ -7525,7 +7546,7 @@
         <v>45.55</v>
       </c>
     </row>
-    <row r="651" spans="1:3">
+    <row r="651" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A651" t="s">
         <v>8</v>
       </c>
@@ -7533,10 +7554,10 @@
         <v>1614.18</v>
       </c>
       <c r="C651">
-        <v>37.09</v>
-      </c>
-    </row>
-    <row r="652" spans="1:3">
+        <v>37.090000000000003</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A652" t="s">
         <v>8</v>
       </c>
@@ -7547,7 +7568,7 @@
         <v>46.96</v>
       </c>
     </row>
-    <row r="653" spans="1:3">
+    <row r="653" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A653" t="s">
         <v>8</v>
       </c>
@@ -7558,7 +7579,7 @@
         <v>43.15</v>
       </c>
     </row>
-    <row r="654" spans="1:3">
+    <row r="654" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A654" t="s">
         <v>8</v>
       </c>
@@ -7569,7 +7590,7 @@
         <v>30.09</v>
       </c>
     </row>
-    <row r="655" spans="1:3">
+    <row r="655" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A655" t="s">
         <v>8</v>
       </c>
@@ -7577,10 +7598,10 @@
         <v>1659.46</v>
       </c>
       <c r="C655">
-        <v>32.63</v>
-      </c>
-    </row>
-    <row r="656" spans="1:3">
+        <v>32.630000000000003</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A656" t="s">
         <v>8</v>
       </c>
@@ -7591,7 +7612,7 @@
         <v>66.47</v>
       </c>
     </row>
-    <row r="657" spans="1:3">
+    <row r="657" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A657" t="s">
         <v>8</v>
       </c>
@@ -7602,7 +7623,7 @@
         <v>50.08</v>
       </c>
     </row>
-    <row r="658" spans="1:3">
+    <row r="658" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A658" t="s">
         <v>8</v>
       </c>
@@ -7613,7 +7634,7 @@
         <v>64.37</v>
       </c>
     </row>
-    <row r="659" spans="1:3">
+    <row r="659" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A659" t="s">
         <v>8</v>
       </c>
@@ -7624,7 +7645,7 @@
         <v>70.53</v>
       </c>
     </row>
-    <row r="660" spans="1:3">
+    <row r="660" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A660" t="s">
         <v>8</v>
       </c>
@@ -7635,7 +7656,7 @@
         <v>53.93</v>
       </c>
     </row>
-    <row r="661" spans="1:3">
+    <row r="661" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A661" t="s">
         <v>8</v>
       </c>
@@ -7643,10 +7664,10 @@
         <v>1784.93</v>
       </c>
       <c r="C661">
-        <v>67.70999999999999</v>
-      </c>
-    </row>
-    <row r="662" spans="1:3">
+        <v>67.709999999999994</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A662" t="s">
         <v>8</v>
       </c>
@@ -7657,7 +7678,7 @@
         <v>44.42</v>
       </c>
     </row>
-    <row r="663" spans="1:3">
+    <row r="663" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A663" t="s">
         <v>8</v>
       </c>
@@ -7668,7 +7689,7 @@
         <v>38.67</v>
       </c>
     </row>
-    <row r="664" spans="1:3">
+    <row r="664" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A664" t="s">
         <v>8</v>
       </c>
@@ -7679,7 +7700,7 @@
         <v>57.13</v>
       </c>
     </row>
-    <row r="665" spans="1:3">
+    <row r="665" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A665" t="s">
         <v>8</v>
       </c>
@@ -7690,7 +7711,7 @@
         <v>40.18</v>
       </c>
     </row>
-    <row r="666" spans="1:3">
+    <row r="666" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A666" t="s">
         <v>8</v>
       </c>
@@ -7701,7 +7722,7 @@
         <v>35.08</v>
       </c>
     </row>
-    <row r="667" spans="1:3">
+    <row r="667" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A667" t="s">
         <v>8</v>
       </c>
@@ -7712,7 +7733,7 @@
         <v>45.77</v>
       </c>
     </row>
-    <row r="668" spans="1:3">
+    <row r="668" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A668" t="s">
         <v>8</v>
       </c>
@@ -7723,7 +7744,7 @@
         <v>45.15</v>
       </c>
     </row>
-    <row r="669" spans="1:3">
+    <row r="669" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A669" t="s">
         <v>8</v>
       </c>
@@ -7731,10 +7752,10 @@
         <v>1810.4</v>
       </c>
       <c r="C669">
-        <v>70.59999999999999</v>
-      </c>
-    </row>
-    <row r="670" spans="1:3">
+        <v>70.599999999999994</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A670" t="s">
         <v>8</v>
       </c>
@@ -7742,10 +7763,10 @@
         <v>1767.76</v>
       </c>
       <c r="C670">
-        <v>66.43000000000001</v>
-      </c>
-    </row>
-    <row r="671" spans="1:3">
+        <v>66.430000000000007</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A671" t="s">
         <v>8</v>
       </c>
@@ -7756,7 +7777,7 @@
         <v>54.99</v>
       </c>
     </row>
-    <row r="672" spans="1:3">
+    <row r="672" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A672" t="s">
         <v>8</v>
       </c>
@@ -7767,7 +7788,7 @@
         <v>65.08</v>
       </c>
     </row>
-    <row r="673" spans="1:3">
+    <row r="673" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A673" t="s">
         <v>8</v>
       </c>
@@ -7775,10 +7796,10 @@
         <v>1653.7</v>
       </c>
       <c r="C673">
-        <v>36.45</v>
-      </c>
-    </row>
-    <row r="674" spans="1:3">
+        <v>36.450000000000003</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A674" t="s">
         <v>8</v>
       </c>
@@ -7789,7 +7810,7 @@
         <v>39.21</v>
       </c>
     </row>
-    <row r="675" spans="1:3">
+    <row r="675" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A675" t="s">
         <v>8</v>
       </c>
@@ -7800,7 +7821,7 @@
         <v>41.22</v>
       </c>
     </row>
-    <row r="676" spans="1:3">
+    <row r="676" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A676" t="s">
         <v>8</v>
       </c>
@@ -7811,7 +7832,7 @@
         <v>53.37</v>
       </c>
     </row>
-    <row r="677" spans="1:3">
+    <row r="677" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A677" t="s">
         <v>8</v>
       </c>
@@ -7822,7 +7843,7 @@
         <v>31.05</v>
       </c>
     </row>
-    <row r="678" spans="1:3">
+    <row r="678" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A678" t="s">
         <v>8</v>
       </c>
@@ -7833,7 +7854,7 @@
         <v>32.43</v>
       </c>
     </row>
-    <row r="679" spans="1:3">
+    <row r="679" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A679" t="s">
         <v>8</v>
       </c>
@@ -7841,10 +7862,10 @@
         <v>1856.61</v>
       </c>
       <c r="C679">
-        <v>40.95</v>
-      </c>
-    </row>
-    <row r="680" spans="1:3">
+        <v>40.950000000000003</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A680" t="s">
         <v>8</v>
       </c>
@@ -7855,7 +7876,7 @@
         <v>31.44</v>
       </c>
     </row>
-    <row r="681" spans="1:3">
+    <row r="681" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A681" t="s">
         <v>8</v>
       </c>
@@ -7866,7 +7887,7 @@
         <v>37.1</v>
       </c>
     </row>
-    <row r="682" spans="1:3">
+    <row r="682" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A682" t="s">
         <v>8</v>
       </c>
@@ -7877,7 +7898,7 @@
         <v>33.07</v>
       </c>
     </row>
-    <row r="683" spans="1:3">
+    <row r="683" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A683" t="s">
         <v>8</v>
       </c>
@@ -7888,7 +7909,7 @@
         <v>42.02</v>
       </c>
     </row>
-    <row r="684" spans="1:3">
+    <row r="684" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A684" t="s">
         <v>8</v>
       </c>
@@ -7899,7 +7920,7 @@
         <v>44.14</v>
       </c>
     </row>
-    <row r="685" spans="1:3">
+    <row r="685" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A685" t="s">
         <v>8</v>
       </c>
@@ -7910,7 +7931,7 @@
         <v>49.73</v>
       </c>
     </row>
-    <row r="686" spans="1:3">
+    <row r="686" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A686" t="s">
         <v>8</v>
       </c>
@@ -7921,7 +7942,7 @@
         <v>56.91</v>
       </c>
     </row>
-    <row r="687" spans="1:3">
+    <row r="687" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A687" t="s">
         <v>8</v>
       </c>
@@ -7929,10 +7950,10 @@
         <v>1692</v>
       </c>
       <c r="C687">
-        <v>38.87</v>
-      </c>
-    </row>
-    <row r="688" spans="1:3">
+        <v>38.869999999999997</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A688" t="s">
         <v>8</v>
       </c>
@@ -7943,7 +7964,7 @@
         <v>44.48</v>
       </c>
     </row>
-    <row r="689" spans="1:3">
+    <row r="689" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A689" t="s">
         <v>8</v>
       </c>
@@ -7954,7 +7975,7 @@
         <v>98.09</v>
       </c>
     </row>
-    <row r="690" spans="1:3">
+    <row r="690" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A690" t="s">
         <v>8</v>
       </c>
@@ -7965,7 +7986,7 @@
         <v>43.14</v>
       </c>
     </row>
-    <row r="691" spans="1:3">
+    <row r="691" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A691" t="s">
         <v>8</v>
       </c>
@@ -7976,7 +7997,7 @@
         <v>72.45</v>
       </c>
     </row>
-    <row r="692" spans="1:3">
+    <row r="692" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A692" t="s">
         <v>8</v>
       </c>
@@ -7987,7 +8008,7 @@
         <v>50.86</v>
       </c>
     </row>
-    <row r="693" spans="1:3">
+    <row r="693" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A693" t="s">
         <v>8</v>
       </c>
@@ -7998,7 +8019,7 @@
         <v>44.62</v>
       </c>
     </row>
-    <row r="694" spans="1:3">
+    <row r="694" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A694" t="s">
         <v>8</v>
       </c>
@@ -8009,7 +8030,7 @@
         <v>101.3</v>
       </c>
     </row>
-    <row r="695" spans="1:3">
+    <row r="695" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A695" t="s">
         <v>8</v>
       </c>
@@ -8020,18 +8041,18 @@
         <v>86.03</v>
       </c>
     </row>
-    <row r="696" spans="1:3">
+    <row r="696" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A696" t="s">
         <v>8</v>
       </c>
       <c r="B696">
-        <v>2568.07</v>
+        <v>2568.0700000000002</v>
       </c>
       <c r="C696">
-        <v>69.79000000000001</v>
-      </c>
-    </row>
-    <row r="697" spans="1:3">
+        <v>69.790000000000006</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A697" t="s">
         <v>8</v>
       </c>
@@ -8042,7 +8063,7 @@
         <v>99.64</v>
       </c>
     </row>
-    <row r="698" spans="1:3">
+    <row r="698" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A698" t="s">
         <v>8</v>
       </c>
@@ -8053,7 +8074,7 @@
         <v>103.8</v>
       </c>
     </row>
-    <row r="699" spans="1:3">
+    <row r="699" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A699" t="s">
         <v>8</v>
       </c>
@@ -8064,7 +8085,7 @@
         <v>79.61</v>
       </c>
     </row>
-    <row r="700" spans="1:3">
+    <row r="700" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A700" t="s">
         <v>8</v>
       </c>
@@ -8072,21 +8093,21 @@
         <v>2728.63</v>
       </c>
       <c r="C700">
-        <v>73.51000000000001</v>
-      </c>
-    </row>
-    <row r="701" spans="1:3">
+        <v>73.510000000000005</v>
+      </c>
+    </row>
+    <row r="701" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A701" t="s">
         <v>8</v>
       </c>
       <c r="B701">
-        <v>2496.95</v>
+        <v>2496.9499999999998</v>
       </c>
       <c r="C701">
         <v>40</v>
       </c>
     </row>
-    <row r="702" spans="1:3">
+    <row r="702" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A702" t="s">
         <v>8</v>
       </c>
@@ -8097,7 +8118,7 @@
         <v>103.27</v>
       </c>
     </row>
-    <row r="703" spans="1:3">
+    <row r="703" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A703" t="s">
         <v>8</v>
       </c>
@@ -8108,7 +8129,7 @@
         <v>92.12</v>
       </c>
     </row>
-    <row r="704" spans="1:3">
+    <row r="704" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A704" t="s">
         <v>8</v>
       </c>
@@ -8119,7 +8140,7 @@
         <v>50.05</v>
       </c>
     </row>
-    <row r="705" spans="1:3">
+    <row r="705" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A705" t="s">
         <v>8</v>
       </c>
@@ -8130,7 +8151,7 @@
         <v>74.27</v>
       </c>
     </row>
-    <row r="706" spans="1:3">
+    <row r="706" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A706" t="s">
         <v>8</v>
       </c>
@@ -8141,18 +8162,18 @@
         <v>59.34</v>
       </c>
     </row>
-    <row r="707" spans="1:3">
+    <row r="707" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A707" t="s">
         <v>8</v>
       </c>
       <c r="B707">
-        <v>2523.43</v>
+        <v>2523.4299999999998</v>
       </c>
       <c r="C707">
-        <v>97.73999999999999</v>
-      </c>
-    </row>
-    <row r="708" spans="1:3">
+        <v>97.74</v>
+      </c>
+    </row>
+    <row r="708" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A708" t="s">
         <v>8</v>
       </c>
@@ -8163,7 +8184,7 @@
         <v>61.51</v>
       </c>
     </row>
-    <row r="709" spans="1:3">
+    <row r="709" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A709" t="s">
         <v>8</v>
       </c>
@@ -8174,7 +8195,7 @@
         <v>52.17</v>
       </c>
     </row>
-    <row r="710" spans="1:3">
+    <row r="710" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A710" t="s">
         <v>8</v>
       </c>
@@ -8185,7 +8206,7 @@
         <v>100.75</v>
       </c>
     </row>
-    <row r="711" spans="1:3">
+    <row r="711" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A711" t="s">
         <v>8</v>
       </c>
@@ -8196,7 +8217,7 @@
         <v>59.81</v>
       </c>
     </row>
-    <row r="712" spans="1:3">
+    <row r="712" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A712" t="s">
         <v>8</v>
       </c>
@@ -8207,7 +8228,7 @@
         <v>48.49</v>
       </c>
     </row>
-    <row r="713" spans="1:3">
+    <row r="713" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A713" t="s">
         <v>8</v>
       </c>
